--- a/research/traditional_assets/database/data/egypt/egypt_tobacco.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_tobacco.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1257257089323421</v>
+        <v>0.1254777010872443</v>
       </c>
       <c r="C2">
-        <v>1741.101391516666</v>
+        <v>1728.318441491374</v>
       </c>
       <c r="D2">
-        <v>1673.101391516666</v>
+        <v>1677.729451491374</v>
       </c>
       <c r="E2">
-        <v>-0.001</v>
+        <v>17.41001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>17.41101</v>
       </c>
       <c r="G2">
         <v>68</v>
@@ -1451,28 +1451,28 @@
         <v>194.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.875773803</v>
       </c>
       <c r="N2">
-        <v>194.4</v>
+        <v>193.524226197</v>
       </c>
       <c r="O2">
-        <v>43.74</v>
+        <v>43.542950894325</v>
       </c>
       <c r="P2">
-        <v>150.66</v>
+        <v>149.981275302675</v>
       </c>
       <c r="Q2">
-        <v>160.46</v>
+        <v>159.781275302675</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1257257089323421</v>
+        <v>0.1263513899871155</v>
       </c>
       <c r="T2">
-        <v>0.5572774141861078</v>
+        <v>0.5616399393981707</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>221.9751256935006</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1254777010872443</v>
+        <v>0.1252296932421465</v>
       </c>
       <c r="C3">
-        <v>1728.318441491374</v>
+        <v>1715.561166361478</v>
       </c>
       <c r="D3">
-        <v>1677.729451491374</v>
+        <v>1682.383186361478</v>
       </c>
       <c r="E3">
-        <v>17.41001</v>
+        <v>34.82102</v>
       </c>
       <c r="F3">
-        <v>17.41101</v>
+        <v>34.82202</v>
       </c>
       <c r="G3">
         <v>68</v>
@@ -1533,28 +1533,28 @@
         <v>194.4</v>
       </c>
       <c r="M3">
-        <v>0.875773803</v>
+        <v>1.751547606</v>
       </c>
       <c r="N3">
-        <v>193.524226197</v>
+        <v>192.648452394</v>
       </c>
       <c r="O3">
-        <v>43.542950894325</v>
+        <v>43.34590178865</v>
       </c>
       <c r="P3">
-        <v>149.981275302675</v>
+        <v>149.30255060535</v>
       </c>
       <c r="Q3">
-        <v>159.781275302675</v>
+        <v>159.10255060535</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1263513899871155</v>
+        <v>0.1269898400430067</v>
       </c>
       <c r="T3">
-        <v>0.5616399393981707</v>
+        <v>0.5660914957370105</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>221.9751256935006</v>
+        <v>110.9875628467503</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1252296932421465</v>
+        <v>0.1249816853970488</v>
       </c>
       <c r="C4">
-        <v>1715.561166361478</v>
+        <v>1702.829780374586</v>
       </c>
       <c r="D4">
-        <v>1682.383186361478</v>
+        <v>1687.062810374586</v>
       </c>
       <c r="E4">
-        <v>34.82102</v>
+        <v>52.23202999999999</v>
       </c>
       <c r="F4">
-        <v>34.82202</v>
+        <v>52.23302999999999</v>
       </c>
       <c r="G4">
         <v>68</v>
@@ -1615,28 +1615,28 @@
         <v>194.4</v>
       </c>
       <c r="M4">
-        <v>1.751547606</v>
+        <v>2.627321408999999</v>
       </c>
       <c r="N4">
-        <v>192.648452394</v>
+        <v>191.772678591</v>
       </c>
       <c r="O4">
-        <v>43.34590178865</v>
+        <v>43.148852682975</v>
       </c>
       <c r="P4">
-        <v>149.30255060535</v>
+        <v>148.623825908025</v>
       </c>
       <c r="Q4">
-        <v>159.10255060535</v>
+        <v>158.423825908025</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1269898400430067</v>
+        <v>0.127641454017576</v>
       </c>
       <c r="T4">
-        <v>0.5660914957370105</v>
+        <v>0.5706348367426304</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>110.9875628467503</v>
+        <v>73.99170856450021</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1249816853970488</v>
+        <v>0.124733677551951</v>
       </c>
       <c r="C5">
-        <v>1702.829780374586</v>
+        <v>1690.12450016871</v>
       </c>
       <c r="D5">
-        <v>1687.062810374586</v>
+        <v>1691.768540168709</v>
       </c>
       <c r="E5">
-        <v>52.23202999999999</v>
+        <v>69.64304</v>
       </c>
       <c r="F5">
-        <v>52.23302999999999</v>
+        <v>69.64404</v>
       </c>
       <c r="G5">
         <v>68</v>
@@ -1697,28 +1697,28 @@
         <v>194.4</v>
       </c>
       <c r="M5">
-        <v>2.627321408999999</v>
+        <v>3.503095212</v>
       </c>
       <c r="N5">
-        <v>191.772678591</v>
+        <v>190.896904788</v>
       </c>
       <c r="O5">
-        <v>43.148852682975</v>
+        <v>42.9518035773</v>
       </c>
       <c r="P5">
-        <v>148.623825908025</v>
+        <v>147.9451012107</v>
       </c>
       <c r="Q5">
-        <v>158.423825908025</v>
+        <v>157.7451012107</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.127641454017576</v>
+        <v>0.1283066432832823</v>
       </c>
       <c r="T5">
-        <v>0.5706348367426304</v>
+        <v>0.5752728306858674</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>73.99170856450021</v>
+        <v>55.49378142337514</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.124733677551951</v>
+        <v>0.1244856697068532</v>
       </c>
       <c r="C6">
-        <v>1690.12450016871</v>
+        <v>1677.445544805699</v>
       </c>
       <c r="D6">
-        <v>1691.768540168709</v>
+        <v>1696.500594805699</v>
       </c>
       <c r="E6">
-        <v>69.64304</v>
+        <v>87.05404999999999</v>
       </c>
       <c r="F6">
-        <v>69.64404</v>
+        <v>87.05504999999999</v>
       </c>
       <c r="G6">
         <v>68</v>
@@ -1779,28 +1779,28 @@
         <v>194.4</v>
       </c>
       <c r="M6">
-        <v>3.503095212</v>
+        <v>4.378869014999999</v>
       </c>
       <c r="N6">
-        <v>190.896904788</v>
+        <v>190.021130985</v>
       </c>
       <c r="O6">
-        <v>42.9518035773</v>
+        <v>42.75475447162501</v>
       </c>
       <c r="P6">
-        <v>147.9451012107</v>
+        <v>147.266376513375</v>
       </c>
       <c r="Q6">
-        <v>157.7451012107</v>
+        <v>157.066376513375</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1283066432832823</v>
+        <v>0.1289858365335297</v>
       </c>
       <c r="T6">
-        <v>0.5752728306858674</v>
+        <v>0.5800084666068569</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>55.49378142337514</v>
+        <v>44.39502513870012</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1244856697068532</v>
+        <v>0.1242376618617554</v>
       </c>
       <c r="C7">
-        <v>1677.445544805699</v>
+        <v>1664.793135805235</v>
       </c>
       <c r="D7">
-        <v>1696.500594805699</v>
+        <v>1701.259195805235</v>
       </c>
       <c r="E7">
-        <v>87.05404999999999</v>
+        <v>104.46506</v>
       </c>
       <c r="F7">
-        <v>87.05504999999999</v>
+        <v>104.46606</v>
       </c>
       <c r="G7">
         <v>68</v>
@@ -1861,28 +1861,28 @@
         <v>194.4</v>
       </c>
       <c r="M7">
-        <v>4.378869014999999</v>
+        <v>5.254642818</v>
       </c>
       <c r="N7">
-        <v>190.021130985</v>
+        <v>189.145357182</v>
       </c>
       <c r="O7">
-        <v>42.75475447162501</v>
+        <v>42.55770536595</v>
       </c>
       <c r="P7">
-        <v>147.266376513375</v>
+        <v>146.58765181605</v>
       </c>
       <c r="Q7">
-        <v>157.066376513375</v>
+        <v>156.38765181605</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1289858365335297</v>
+        <v>0.1296794807039952</v>
       </c>
       <c r="T7">
-        <v>0.5800084666068569</v>
+        <v>0.5848448607389312</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>44.39502513870012</v>
+        <v>36.99585428225009</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1242376618617554</v>
+        <v>0.1239896540166577</v>
       </c>
       <c r="C8">
-        <v>1664.793135805235</v>
+        <v>1652.167497179398</v>
       </c>
       <c r="D8">
-        <v>1701.259195805235</v>
+        <v>1706.044567179398</v>
       </c>
       <c r="E8">
-        <v>104.46506</v>
+        <v>121.87607</v>
       </c>
       <c r="F8">
-        <v>104.46606</v>
+        <v>121.87707</v>
       </c>
       <c r="G8">
         <v>68</v>
@@ -1943,28 +1943,28 @@
         <v>194.4</v>
       </c>
       <c r="M8">
-        <v>5.254642817999999</v>
+        <v>6.130416620999998</v>
       </c>
       <c r="N8">
-        <v>189.145357182</v>
+        <v>188.269583379</v>
       </c>
       <c r="O8">
-        <v>42.55770536595</v>
+        <v>42.360656260275</v>
       </c>
       <c r="P8">
-        <v>146.58765181605</v>
+        <v>145.908927118725</v>
       </c>
       <c r="Q8">
-        <v>156.38765181605</v>
+        <v>155.708927118725</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1296794807039952</v>
+        <v>0.1303880419533953</v>
       </c>
       <c r="T8">
-        <v>0.5848448607389312</v>
+        <v>0.589785263346964</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.9958542822501</v>
+        <v>31.71073224192866</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1239896540166577</v>
+        <v>0.1237416461715599</v>
       </c>
       <c r="C9">
-        <v>1652.167497179398</v>
+        <v>1639.568855467817</v>
       </c>
       <c r="D9">
-        <v>1706.044567179398</v>
+        <v>1710.856935467817</v>
       </c>
       <c r="E9">
-        <v>121.87607</v>
+        <v>139.28708</v>
       </c>
       <c r="F9">
-        <v>121.87707</v>
+        <v>139.28808</v>
       </c>
       <c r="G9">
         <v>68</v>
@@ -2025,28 +2025,28 @@
         <v>194.4</v>
       </c>
       <c r="M9">
-        <v>6.130416621</v>
+        <v>7.006190424</v>
       </c>
       <c r="N9">
-        <v>188.269583379</v>
+        <v>187.393809576</v>
       </c>
       <c r="O9">
-        <v>42.360656260275</v>
+        <v>42.1636071546</v>
       </c>
       <c r="P9">
-        <v>145.908927118725</v>
+        <v>145.2302024214</v>
       </c>
       <c r="Q9">
-        <v>155.708927118725</v>
+        <v>155.0302024214</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1303880419533953</v>
+        <v>0.1311120067082173</v>
       </c>
       <c r="T9">
-        <v>0.589785263346964</v>
+        <v>0.5948330660116933</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.71073224192865</v>
+        <v>27.74689071168757</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1237416461715599</v>
+        <v>0.1234936383264622</v>
       </c>
       <c r="C10">
-        <v>1639.568855467817</v>
+        <v>1626.997439773424</v>
       </c>
       <c r="D10">
-        <v>1710.856935467817</v>
+        <v>1715.696529773424</v>
       </c>
       <c r="E10">
-        <v>139.28708</v>
+        <v>156.69809</v>
       </c>
       <c r="F10">
-        <v>139.28808</v>
+        <v>156.69909</v>
       </c>
       <c r="G10">
         <v>68</v>
@@ -2107,28 +2107,28 @@
         <v>194.4</v>
       </c>
       <c r="M10">
-        <v>7.006190424</v>
+        <v>7.881964226999999</v>
       </c>
       <c r="N10">
-        <v>187.393809576</v>
+        <v>186.518035773</v>
       </c>
       <c r="O10">
-        <v>42.1636071546</v>
+        <v>41.966558048925</v>
       </c>
       <c r="P10">
-        <v>145.2302024214</v>
+        <v>144.551477724075</v>
       </c>
       <c r="Q10">
-        <v>155.0302024214</v>
+        <v>154.351477724075</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1311120067082173</v>
+        <v>0.131851882776332</v>
       </c>
       <c r="T10">
-        <v>0.5948330660116933</v>
+        <v>0.5999918093943286</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.74689071168757</v>
+        <v>24.6639028548334</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1234936383264622</v>
+        <v>0.1232456304813644</v>
       </c>
       <c r="C11">
-        <v>1626.997439773424</v>
+        <v>1614.453481798807</v>
       </c>
       <c r="D11">
-        <v>1715.696529773424</v>
+        <v>1720.563581798807</v>
       </c>
       <c r="E11">
-        <v>156.69809</v>
+        <v>174.1091</v>
       </c>
       <c r="F11">
-        <v>156.69909</v>
+        <v>174.1101</v>
       </c>
       <c r="G11">
         <v>68</v>
@@ -2189,28 +2189,28 @@
         <v>194.4</v>
       </c>
       <c r="M11">
-        <v>7.881964226999999</v>
+        <v>8.757738029999997</v>
       </c>
       <c r="N11">
-        <v>186.518035773</v>
+        <v>185.64226197</v>
       </c>
       <c r="O11">
-        <v>41.966558048925</v>
+        <v>41.76950894325</v>
       </c>
       <c r="P11">
-        <v>144.551477724075</v>
+        <v>143.87275302675</v>
       </c>
       <c r="Q11">
-        <v>154.351477724075</v>
+        <v>153.67275302675</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.131851882776332</v>
+        <v>0.1326082005348493</v>
       </c>
       <c r="T11">
-        <v>0.5999918093943286</v>
+        <v>0.6052651915188003</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.6639028548334</v>
+        <v>22.19751256935007</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1232456304813644</v>
+        <v>0.1229976226362666</v>
       </c>
       <c r="C12">
-        <v>1614.453481798807</v>
+        <v>1601.937215883189</v>
       </c>
       <c r="D12">
-        <v>1720.563581798807</v>
+        <v>1725.458325883189</v>
       </c>
       <c r="E12">
-        <v>174.1091</v>
+        <v>191.52011</v>
       </c>
       <c r="F12">
-        <v>174.1101</v>
+        <v>191.52111</v>
       </c>
       <c r="G12">
         <v>68</v>
@@ -2271,28 +2271,28 @@
         <v>194.4</v>
       </c>
       <c r="M12">
-        <v>8.757738029999999</v>
+        <v>9.633511833</v>
       </c>
       <c r="N12">
-        <v>185.64226197</v>
+        <v>184.766488167</v>
       </c>
       <c r="O12">
-        <v>41.76950894325</v>
+        <v>41.572459837575</v>
       </c>
       <c r="P12">
-        <v>143.87275302675</v>
+        <v>143.194028329425</v>
       </c>
       <c r="Q12">
-        <v>153.67275302675</v>
+        <v>152.994028329425</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1326082005348493</v>
+        <v>0.1333815141980524</v>
       </c>
       <c r="T12">
-        <v>0.6052651915188003</v>
+        <v>0.6106570766123612</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.19751256935006</v>
+        <v>20.17955688122732</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1229976226362666</v>
+        <v>0.1227496147911688</v>
       </c>
       <c r="C13">
-        <v>1601.937215883189</v>
+        <v>1589.448879040041</v>
       </c>
       <c r="D13">
-        <v>1725.458325883189</v>
+        <v>1730.38099904004</v>
       </c>
       <c r="E13">
-        <v>191.52011</v>
+        <v>208.93112</v>
       </c>
       <c r="F13">
-        <v>191.52111</v>
+        <v>208.93212</v>
       </c>
       <c r="G13">
         <v>68</v>
@@ -2353,28 +2353,28 @@
         <v>194.4</v>
       </c>
       <c r="M13">
-        <v>9.633511833</v>
+        <v>10.509285636</v>
       </c>
       <c r="N13">
-        <v>184.766488167</v>
+        <v>183.890714364</v>
       </c>
       <c r="O13">
-        <v>41.572459837575</v>
+        <v>41.3754107319</v>
       </c>
       <c r="P13">
-        <v>143.194028329425</v>
+        <v>142.5153036321</v>
       </c>
       <c r="Q13">
-        <v>152.994028329425</v>
+        <v>152.3153036321</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1333815141980524</v>
+        <v>0.1341724031717828</v>
       </c>
       <c r="T13">
-        <v>0.6106570766123612</v>
+        <v>0.6161715045489579</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.17955688122732</v>
+        <v>18.49792714112505</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1227496147911688</v>
+        <v>0.1225016069460711</v>
       </c>
       <c r="C14">
-        <v>1589.448879040041</v>
+        <v>1576.988710995337</v>
       </c>
       <c r="D14">
-        <v>1730.38099904004</v>
+        <v>1735.331840995337</v>
       </c>
       <c r="E14">
-        <v>208.93112</v>
+        <v>226.34213</v>
       </c>
       <c r="F14">
-        <v>208.93212</v>
+        <v>226.34313</v>
       </c>
       <c r="G14">
         <v>68</v>
@@ -2435,28 +2435,28 @@
         <v>194.4</v>
       </c>
       <c r="M14">
-        <v>10.509285636</v>
+        <v>11.385059439</v>
       </c>
       <c r="N14">
-        <v>183.890714364</v>
+        <v>183.014940561</v>
       </c>
       <c r="O14">
-        <v>41.3754107319</v>
+        <v>41.178361626225</v>
       </c>
       <c r="P14">
-        <v>142.5153036321</v>
+        <v>141.836578934775</v>
       </c>
       <c r="Q14">
-        <v>152.3153036321</v>
+        <v>151.636578934775</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1341724031717828</v>
+        <v>0.1349814735012311</v>
       </c>
       <c r="T14">
-        <v>0.6161715045489579</v>
+        <v>0.6218127009438669</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.49792714112505</v>
+        <v>17.07500966873081</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1225016069460711</v>
+        <v>0.1222535991009733</v>
       </c>
       <c r="C15">
-        <v>1576.988710995337</v>
+        <v>1564.556954226472</v>
       </c>
       <c r="D15">
-        <v>1735.331840995337</v>
+        <v>1740.311094226472</v>
       </c>
       <c r="E15">
-        <v>226.34213</v>
+        <v>243.75314</v>
       </c>
       <c r="F15">
-        <v>226.34313</v>
+        <v>243.75414</v>
       </c>
       <c r="G15">
         <v>68</v>
@@ -2517,28 +2517,28 @@
         <v>194.4</v>
       </c>
       <c r="M15">
-        <v>11.385059439</v>
+        <v>12.260833242</v>
       </c>
       <c r="N15">
-        <v>183.014940561</v>
+        <v>182.139166758</v>
       </c>
       <c r="O15">
-        <v>41.178361626225</v>
+        <v>40.98131252055001</v>
       </c>
       <c r="P15">
-        <v>141.836578934775</v>
+        <v>141.15785423745</v>
       </c>
       <c r="Q15">
-        <v>151.636578934775</v>
+        <v>150.95785423745</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1349814735012311</v>
+        <v>0.1358093594197364</v>
       </c>
       <c r="T15">
-        <v>0.6218127009438669</v>
+        <v>0.6275850879526108</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.07500966873081</v>
+        <v>15.85536612096433</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1222535991009733</v>
+        <v>0.1220055912558755</v>
       </c>
       <c r="C16">
-        <v>1564.556954226472</v>
+        <v>1552.153854001845</v>
       </c>
       <c r="D16">
-        <v>1740.311094226472</v>
+        <v>1745.319004001845</v>
       </c>
       <c r="E16">
-        <v>243.75314</v>
+        <v>261.1641500000001</v>
       </c>
       <c r="F16">
-        <v>243.75414</v>
+        <v>261.16515</v>
       </c>
       <c r="G16">
         <v>68</v>
@@ -2599,28 +2599,28 @@
         <v>194.4</v>
       </c>
       <c r="M16">
-        <v>12.260833242</v>
+        <v>13.136607045</v>
       </c>
       <c r="N16">
-        <v>182.139166758</v>
+        <v>181.263392955</v>
       </c>
       <c r="O16">
-        <v>40.98131252055001</v>
+        <v>40.784263414875</v>
       </c>
       <c r="P16">
-        <v>141.15785423745</v>
+        <v>140.479129540125</v>
       </c>
       <c r="Q16">
-        <v>150.95785423745</v>
+        <v>150.279129540125</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1358093594197364</v>
+        <v>0.1366567250069124</v>
       </c>
       <c r="T16">
-        <v>0.6275850879526108</v>
+        <v>0.633493295832149</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.85536612096433</v>
+        <v>14.79834171290004</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1220055912558755</v>
+        <v>0.1217575834107777</v>
       </c>
       <c r="C17">
-        <v>1552.153854001845</v>
+        <v>1539.779658421137</v>
       </c>
       <c r="D17">
-        <v>1745.319004001845</v>
+        <v>1750.355818421137</v>
       </c>
       <c r="E17">
-        <v>261.16415</v>
+        <v>278.57516</v>
       </c>
       <c r="F17">
-        <v>261.16515</v>
+        <v>278.57616</v>
       </c>
       <c r="G17">
         <v>68</v>
@@ -2681,28 +2681,28 @@
         <v>194.4</v>
       </c>
       <c r="M17">
-        <v>13.136607045</v>
+        <v>14.012380848</v>
       </c>
       <c r="N17">
-        <v>181.263392955</v>
+        <v>180.387619152</v>
       </c>
       <c r="O17">
-        <v>40.784263414875</v>
+        <v>40.58721430920001</v>
       </c>
       <c r="P17">
-        <v>140.479129540125</v>
+        <v>139.8004048428</v>
       </c>
       <c r="Q17">
-        <v>150.279129540125</v>
+        <v>149.6004048428</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1366567250069124</v>
+        <v>0.1375242659652116</v>
       </c>
       <c r="T17">
-        <v>0.633493295832149</v>
+        <v>0.6395421753278665</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.79834171290004</v>
+        <v>13.87344535584379</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1217575834107777</v>
+        <v>0.12150957556568</v>
       </c>
       <c r="C18">
-        <v>1539.779658421137</v>
+        <v>1527.434618456277</v>
       </c>
       <c r="D18">
-        <v>1750.355818421137</v>
+        <v>1755.421788456277</v>
       </c>
       <c r="E18">
-        <v>278.57516</v>
+        <v>295.98617</v>
       </c>
       <c r="F18">
-        <v>278.57616</v>
+        <v>295.98717</v>
       </c>
       <c r="G18">
         <v>68</v>
@@ -2763,28 +2763,28 @@
         <v>194.4</v>
       </c>
       <c r="M18">
-        <v>14.012380848</v>
+        <v>14.888154651</v>
       </c>
       <c r="N18">
-        <v>180.387619152</v>
+        <v>179.511845349</v>
       </c>
       <c r="O18">
-        <v>40.58721430920001</v>
+        <v>40.390165203525</v>
       </c>
       <c r="P18">
-        <v>139.8004048428</v>
+        <v>139.121680145475</v>
       </c>
       <c r="Q18">
-        <v>149.6004048428</v>
+        <v>148.921680145475</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1375242659652116</v>
+        <v>0.1384127115249156</v>
       </c>
       <c r="T18">
-        <v>0.6395421753278665</v>
+        <v>0.645736810956011</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.87344535584379</v>
+        <v>13.0573603349118</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.12150957556568</v>
+        <v>0.1214708177205822</v>
       </c>
       <c r="C19">
-        <v>1527.434618456277</v>
+        <v>1510.817952128066</v>
       </c>
       <c r="D19">
-        <v>1755.421788456277</v>
+        <v>1756.216132128066</v>
       </c>
       <c r="E19">
-        <v>295.98617</v>
+        <v>313.39718</v>
       </c>
       <c r="F19">
-        <v>295.98717</v>
+        <v>313.39818</v>
       </c>
       <c r="G19">
         <v>68</v>
@@ -2845,45 +2845,45 @@
         <v>194.4</v>
       </c>
       <c r="M19">
-        <v>14.888154651</v>
+        <v>16.234025724</v>
       </c>
       <c r="N19">
-        <v>179.511845349</v>
+        <v>178.165974276</v>
       </c>
       <c r="O19">
-        <v>40.390165203525</v>
+        <v>40.08734421210001</v>
       </c>
       <c r="P19">
-        <v>139.121680145475</v>
+        <v>138.0786300639</v>
       </c>
       <c r="Q19">
-        <v>148.921680145475</v>
+        <v>147.8786300639</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1384127115249156</v>
+        <v>0.1393228264885149</v>
       </c>
       <c r="T19">
-        <v>0.645736810956011</v>
+        <v>0.6520825352580127</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.225</v>
       </c>
       <c r="W19">
-        <v>0.0389825</v>
+        <v>0.040145</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.0573603349118</v>
+        <v>11.97484858685444</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1214708177205822</v>
+        <v>0.1212344348754845</v>
       </c>
       <c r="C20">
-        <v>1510.817952128066</v>
+        <v>1498.267224359965</v>
       </c>
       <c r="D20">
-        <v>1756.216132128066</v>
+        <v>1761.076414359965</v>
       </c>
       <c r="E20">
-        <v>313.39718</v>
+        <v>330.80819</v>
       </c>
       <c r="F20">
-        <v>313.39818</v>
+        <v>330.80919</v>
       </c>
       <c r="G20">
         <v>68</v>
@@ -2927,28 +2927,28 @@
         <v>194.4</v>
       </c>
       <c r="M20">
-        <v>16.234025724</v>
+        <v>17.135916042</v>
       </c>
       <c r="N20">
-        <v>178.165974276</v>
+        <v>177.264083958</v>
       </c>
       <c r="O20">
-        <v>40.08734421210001</v>
+        <v>39.88441889055</v>
       </c>
       <c r="P20">
-        <v>138.0786300639</v>
+        <v>137.37966506745</v>
       </c>
       <c r="Q20">
-        <v>147.8786300639</v>
+        <v>147.17966506745</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1393228264885149</v>
+        <v>0.140255413426524</v>
       </c>
       <c r="T20">
-        <v>0.6520825352580127</v>
+        <v>0.658584944110681</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.97484858685444</v>
+        <v>11.34459339807263</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1212344348754845</v>
+        <v>0.1209980520303867</v>
       </c>
       <c r="C21">
-        <v>1498.267224359965</v>
+        <v>1485.743472655438</v>
       </c>
       <c r="D21">
-        <v>1761.076414359965</v>
+        <v>1765.963672655438</v>
       </c>
       <c r="E21">
-        <v>330.80819</v>
+        <v>348.2192</v>
       </c>
       <c r="F21">
-        <v>330.80919</v>
+        <v>348.2202</v>
       </c>
       <c r="G21">
         <v>68</v>
@@ -3009,28 +3009,28 @@
         <v>194.4</v>
       </c>
       <c r="M21">
-        <v>17.135916042</v>
+        <v>18.03780636</v>
       </c>
       <c r="N21">
-        <v>177.264083958</v>
+        <v>176.36219364</v>
       </c>
       <c r="O21">
-        <v>39.88441889055</v>
+        <v>39.681493569</v>
       </c>
       <c r="P21">
-        <v>137.37966506745</v>
+        <v>136.680700071</v>
       </c>
       <c r="Q21">
-        <v>147.17966506745</v>
+        <v>146.480700071</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.140255413426524</v>
+        <v>0.1412113150379834</v>
       </c>
       <c r="T21">
-        <v>0.658584944110681</v>
+        <v>0.6652499131846662</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.34459339807263</v>
+        <v>10.777363728169</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1209980520303867</v>
+        <v>0.1207616691852889</v>
       </c>
       <c r="C22">
-        <v>1485.743472655438</v>
+        <v>1473.246922227681</v>
       </c>
       <c r="D22">
-        <v>1765.963672655438</v>
+        <v>1770.878132227681</v>
       </c>
       <c r="E22">
-        <v>348.2192</v>
+        <v>365.63021</v>
       </c>
       <c r="F22">
-        <v>348.2202</v>
+        <v>365.63121</v>
       </c>
       <c r="G22">
         <v>68</v>
@@ -3091,28 +3091,28 @@
         <v>194.4</v>
       </c>
       <c r="M22">
-        <v>18.03780636</v>
+        <v>18.939696678</v>
       </c>
       <c r="N22">
-        <v>176.36219364</v>
+        <v>175.460303322</v>
       </c>
       <c r="O22">
-        <v>39.681493569</v>
+        <v>39.47856824745001</v>
       </c>
       <c r="P22">
-        <v>136.680700071</v>
+        <v>135.98173507455</v>
       </c>
       <c r="Q22">
-        <v>146.480700071</v>
+        <v>145.78173507455</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1412113150379834</v>
+        <v>0.1421914166902391</v>
       </c>
       <c r="T22">
-        <v>0.6652499131846662</v>
+        <v>0.6720836156529293</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.777363728169</v>
+        <v>10.26415593158952</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1207616691852889</v>
+        <v>0.1208151363401912</v>
       </c>
       <c r="C23">
-        <v>1473.246922227681</v>
+        <v>1454.721924227353</v>
       </c>
       <c r="D23">
-        <v>1770.878132227681</v>
+        <v>1769.764144227353</v>
       </c>
       <c r="E23">
-        <v>365.63021</v>
+        <v>383.04122</v>
       </c>
       <c r="F23">
-        <v>365.63121</v>
+        <v>383.04222</v>
       </c>
       <c r="G23">
         <v>68</v>
@@ -3173,45 +3173,45 @@
         <v>194.4</v>
       </c>
       <c r="M23">
-        <v>18.939696678</v>
+        <v>20.49275877</v>
       </c>
       <c r="N23">
-        <v>175.460303322</v>
+        <v>173.90724123</v>
       </c>
       <c r="O23">
-        <v>39.47856824745001</v>
+        <v>39.12912927675001</v>
       </c>
       <c r="P23">
-        <v>135.98173507455</v>
+        <v>134.77811195325</v>
       </c>
       <c r="Q23">
-        <v>145.78173507455</v>
+        <v>144.57811195325</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1421914166902391</v>
+        <v>0.1431966491540912</v>
       </c>
       <c r="T23">
-        <v>0.6720836156529293</v>
+        <v>0.6790925412614045</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.225</v>
       </c>
       <c r="W23">
-        <v>0.040145</v>
+        <v>0.0414625</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>10.26415593158952</v>
+        <v>9.486277674072285</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1208151363401912</v>
+        <v>0.1205919284950934</v>
       </c>
       <c r="C24">
-        <v>1454.721924227353</v>
+        <v>1441.970760804296</v>
       </c>
       <c r="D24">
-        <v>1769.764144227353</v>
+        <v>1774.423990804296</v>
       </c>
       <c r="E24">
-        <v>383.04122</v>
+        <v>400.45223</v>
       </c>
       <c r="F24">
-        <v>383.04222</v>
+        <v>400.45323</v>
       </c>
       <c r="G24">
         <v>68</v>
@@ -3255,28 +3255,28 @@
         <v>194.4</v>
       </c>
       <c r="M24">
-        <v>20.49275877</v>
+        <v>21.424247805</v>
       </c>
       <c r="N24">
-        <v>173.90724123</v>
+        <v>172.975752195</v>
       </c>
       <c r="O24">
-        <v>39.12912927675001</v>
+        <v>38.919544243875</v>
       </c>
       <c r="P24">
-        <v>134.77811195325</v>
+        <v>134.056207951125</v>
       </c>
       <c r="Q24">
-        <v>144.57811195325</v>
+        <v>143.856207951125</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1431966491540912</v>
+        <v>0.1442279915520693</v>
       </c>
       <c r="T24">
-        <v>0.6790925412614045</v>
+        <v>0.686283516885684</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.486277674072285</v>
+        <v>9.073830818677838</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1205919284950934</v>
+        <v>0.1203687206499956</v>
       </c>
       <c r="C25">
-        <v>1441.970760804296</v>
+        <v>1429.244201219267</v>
       </c>
       <c r="D25">
-        <v>1774.423990804296</v>
+        <v>1779.108441219267</v>
       </c>
       <c r="E25">
-        <v>400.45223</v>
+        <v>417.86324</v>
       </c>
       <c r="F25">
-        <v>400.45323</v>
+        <v>417.86424</v>
       </c>
       <c r="G25">
         <v>68</v>
@@ -3337,28 +3337,28 @@
         <v>194.4</v>
       </c>
       <c r="M25">
-        <v>21.424247805</v>
+        <v>22.35573684</v>
       </c>
       <c r="N25">
-        <v>172.975752195</v>
+        <v>172.04426316</v>
       </c>
       <c r="O25">
-        <v>38.919544243875</v>
+        <v>38.709959211</v>
       </c>
       <c r="P25">
-        <v>134.056207951125</v>
+        <v>133.334303949</v>
       </c>
       <c r="Q25">
-        <v>143.856207951125</v>
+        <v>143.134303949</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1442279915520693</v>
+        <v>0.1452864745394679</v>
       </c>
       <c r="T25">
-        <v>0.686283516885684</v>
+        <v>0.6936637287106026</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.073830818677838</v>
+        <v>8.695754534566262</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1203687206499956</v>
+        <v>0.1201455128048978</v>
       </c>
       <c r="C26">
-        <v>1429.244201219267</v>
+        <v>1416.542440849251</v>
       </c>
       <c r="D26">
-        <v>1779.108441219267</v>
+        <v>1783.817690849251</v>
       </c>
       <c r="E26">
-        <v>417.86324</v>
+        <v>435.27425</v>
       </c>
       <c r="F26">
-        <v>417.8642399999999</v>
+        <v>435.27525</v>
       </c>
       <c r="G26">
         <v>68</v>
@@ -3419,28 +3419,28 @@
         <v>194.4</v>
       </c>
       <c r="M26">
-        <v>22.35573684</v>
+        <v>23.287225875</v>
       </c>
       <c r="N26">
-        <v>172.04426316</v>
+        <v>171.112774125</v>
       </c>
       <c r="O26">
-        <v>38.709959211</v>
+        <v>38.50037417812501</v>
       </c>
       <c r="P26">
-        <v>133.334303949</v>
+        <v>132.612399946875</v>
       </c>
       <c r="Q26">
-        <v>143.134303949</v>
+        <v>142.412399946875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1452864745394679</v>
+        <v>0.1463731837398638</v>
       </c>
       <c r="T26">
-        <v>0.6936637287106026</v>
+        <v>0.7012407461841856</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.695754534566262</v>
+        <v>8.347924353183611</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1201455128048978</v>
+        <v>0.1199223049598001</v>
       </c>
       <c r="C27">
-        <v>1416.542440849251</v>
+        <v>1403.865677145355</v>
       </c>
       <c r="D27">
-        <v>1783.817690849251</v>
+        <v>1788.551937145355</v>
       </c>
       <c r="E27">
-        <v>435.27425</v>
+        <v>452.68526</v>
       </c>
       <c r="F27">
-        <v>435.27525</v>
+        <v>452.68626</v>
       </c>
       <c r="G27">
         <v>68</v>
@@ -3501,28 +3501,28 @@
         <v>194.4</v>
       </c>
       <c r="M27">
-        <v>23.287225875</v>
+        <v>24.21871491</v>
       </c>
       <c r="N27">
-        <v>171.112774125</v>
+        <v>170.18128509</v>
       </c>
       <c r="O27">
-        <v>38.50037417812501</v>
+        <v>38.29078914525</v>
       </c>
       <c r="P27">
-        <v>132.612399946875</v>
+        <v>131.89049594475</v>
       </c>
       <c r="Q27">
-        <v>142.412399946875</v>
+        <v>141.69049594475</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1463731837398638</v>
+        <v>0.1474892634591893</v>
       </c>
       <c r="T27">
-        <v>0.7012407461841856</v>
+        <v>0.7090225479138115</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.347924353183611</v>
+        <v>8.026850339599626</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1199223049598001</v>
+        <v>0.1196990971147023</v>
       </c>
       <c r="C28">
-        <v>1403.865677145355</v>
+        <v>1391.214109660401</v>
       </c>
       <c r="D28">
-        <v>1788.551937145355</v>
+        <v>1793.311379660401</v>
       </c>
       <c r="E28">
-        <v>452.68526</v>
+        <v>470.09627</v>
       </c>
       <c r="F28">
-        <v>452.68626</v>
+        <v>470.09727</v>
       </c>
       <c r="G28">
         <v>68</v>
@@ -3583,28 +3583,28 @@
         <v>194.4</v>
       </c>
       <c r="M28">
-        <v>24.21871491</v>
+        <v>25.150203945</v>
       </c>
       <c r="N28">
-        <v>170.18128509</v>
+        <v>169.249796055</v>
       </c>
       <c r="O28">
-        <v>38.29078914525</v>
+        <v>38.081204112375</v>
       </c>
       <c r="P28">
-        <v>131.89049594475</v>
+        <v>131.168591942625</v>
       </c>
       <c r="Q28">
-        <v>141.69049594475</v>
+        <v>140.968591942625</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1474892634591893</v>
+        <v>0.1486359207050716</v>
       </c>
       <c r="T28">
-        <v>0.7090225479138115</v>
+        <v>0.7170175496908243</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.026850339599626</v>
+        <v>7.729559586281121</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1196990971147023</v>
+        <v>0.1196494892696045</v>
       </c>
       <c r="C29">
-        <v>1391.214109660401</v>
+        <v>1374.864326115118</v>
       </c>
       <c r="D29">
-        <v>1793.311379660401</v>
+        <v>1794.372606115118</v>
       </c>
       <c r="E29">
-        <v>470.09627</v>
+        <v>487.50728</v>
       </c>
       <c r="F29">
-        <v>470.09727</v>
+        <v>487.50828</v>
       </c>
       <c r="G29">
         <v>68</v>
@@ -3665,45 +3665,45 @@
         <v>194.4</v>
       </c>
       <c r="M29">
-        <v>25.150203945</v>
+        <v>26.471699604</v>
       </c>
       <c r="N29">
-        <v>169.249796055</v>
+        <v>167.928300396</v>
       </c>
       <c r="O29">
-        <v>38.081204112375</v>
+        <v>37.7838675891</v>
       </c>
       <c r="P29">
-        <v>131.168591942625</v>
+        <v>130.1444328069</v>
       </c>
       <c r="Q29">
-        <v>140.968591942625</v>
+        <v>139.9444328069</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1486359207050716</v>
+        <v>0.1498144295411174</v>
       </c>
       <c r="T29">
-        <v>0.7170175496908243</v>
+        <v>0.725234634850532</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.225</v>
       </c>
       <c r="W29">
-        <v>0.0414625</v>
+        <v>0.0420825</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.729559586281121</v>
+        <v>7.343691674811285</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1196494892696045</v>
+        <v>0.1194324814245068</v>
       </c>
       <c r="C30">
-        <v>1374.864326115118</v>
+        <v>1362.110418337181</v>
       </c>
       <c r="D30">
-        <v>1794.372606115118</v>
+        <v>1799.029708337181</v>
       </c>
       <c r="E30">
-        <v>487.50728</v>
+        <v>504.9182900000001</v>
       </c>
       <c r="F30">
-        <v>487.50828</v>
+        <v>504.91929</v>
       </c>
       <c r="G30">
         <v>68</v>
@@ -3747,28 +3747,28 @@
         <v>194.4</v>
       </c>
       <c r="M30">
-        <v>26.471699604</v>
+        <v>27.417117447</v>
       </c>
       <c r="N30">
-        <v>167.928300396</v>
+        <v>166.982882553</v>
       </c>
       <c r="O30">
-        <v>37.7838675891</v>
+        <v>37.571148574425</v>
       </c>
       <c r="P30">
-        <v>130.1444328069</v>
+        <v>129.411733978575</v>
       </c>
       <c r="Q30">
-        <v>139.9444328069</v>
+        <v>139.211733978575</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1498144295411174</v>
+        <v>0.1510261358091645</v>
       </c>
       <c r="T30">
-        <v>0.725234634850532</v>
+        <v>0.7336831871978371</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.343691674811285</v>
+        <v>7.090460927403999</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1194324814245067</v>
+        <v>0.119215473579409</v>
       </c>
       <c r="C31">
-        <v>1362.110418337182</v>
+        <v>1349.380747485236</v>
       </c>
       <c r="D31">
-        <v>1799.029708337182</v>
+        <v>1803.711047485236</v>
       </c>
       <c r="E31">
-        <v>504.91829</v>
+        <v>522.3293</v>
       </c>
       <c r="F31">
-        <v>504.9192899999999</v>
+        <v>522.3303</v>
       </c>
       <c r="G31">
         <v>68</v>
@@ -3829,28 +3829,28 @@
         <v>194.4</v>
       </c>
       <c r="M31">
-        <v>27.417117447</v>
+        <v>28.36253529</v>
       </c>
       <c r="N31">
-        <v>166.982882553</v>
+        <v>166.03746471</v>
       </c>
       <c r="O31">
-        <v>37.57114857442501</v>
+        <v>37.35842955975</v>
       </c>
       <c r="P31">
-        <v>129.411733978575</v>
+        <v>128.67903515025</v>
       </c>
       <c r="Q31">
-        <v>139.211733978575</v>
+        <v>138.47903515025</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1510261358091644</v>
+        <v>0.1522724622562986</v>
       </c>
       <c r="T31">
-        <v>0.733683187197837</v>
+        <v>0.7423731267550651</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.090460927404002</v>
+        <v>6.854112229823866</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.119215473579409</v>
+        <v>0.1189984657343112</v>
       </c>
       <c r="C32">
-        <v>1349.380747485236</v>
+        <v>1336.675503257011</v>
       </c>
       <c r="D32">
-        <v>1803.711047485236</v>
+        <v>1808.416813257011</v>
       </c>
       <c r="E32">
-        <v>522.3293</v>
+        <v>539.74031</v>
       </c>
       <c r="F32">
-        <v>522.3303</v>
+        <v>539.74131</v>
       </c>
       <c r="G32">
         <v>68</v>
@@ -3911,28 +3911,28 @@
         <v>194.4</v>
       </c>
       <c r="M32">
-        <v>28.36253529</v>
+        <v>29.307953133</v>
       </c>
       <c r="N32">
-        <v>166.03746471</v>
+        <v>165.092046867</v>
       </c>
       <c r="O32">
-        <v>37.35842955975</v>
+        <v>37.145710545075</v>
       </c>
       <c r="P32">
-        <v>128.67903515025</v>
+        <v>127.946336321925</v>
       </c>
       <c r="Q32">
-        <v>138.47903515025</v>
+        <v>137.746336321925</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1522724622562986</v>
+        <v>0.1535549141076974</v>
       </c>
       <c r="T32">
-        <v>0.7423731267550651</v>
+        <v>0.7513149486182996</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.854112229823866</v>
+        <v>6.633011835313418</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1189984657343112</v>
+        <v>0.1187814578892134</v>
       </c>
       <c r="C33">
-        <v>1336.675503257011</v>
+        <v>1323.994877335052</v>
       </c>
       <c r="D33">
-        <v>1808.416813257011</v>
+        <v>1813.147197335052</v>
       </c>
       <c r="E33">
-        <v>539.74031</v>
+        <v>557.1513200000001</v>
       </c>
       <c r="F33">
-        <v>539.74131</v>
+        <v>557.15232</v>
       </c>
       <c r="G33">
         <v>68</v>
@@ -3993,28 +3993,28 @@
         <v>194.4</v>
       </c>
       <c r="M33">
-        <v>29.307953133</v>
+        <v>30.253370976</v>
       </c>
       <c r="N33">
-        <v>165.092046867</v>
+        <v>164.146629024</v>
       </c>
       <c r="O33">
-        <v>37.145710545075</v>
+        <v>36.9329915304</v>
       </c>
       <c r="P33">
-        <v>127.946336321925</v>
+        <v>127.2136374936</v>
       </c>
       <c r="Q33">
-        <v>137.746336321925</v>
+        <v>137.0136374936</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1535549141076974</v>
+        <v>0.1548750851311962</v>
       </c>
       <c r="T33">
-        <v>0.7513149486182996</v>
+        <v>0.7605197652422176</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.633011835313418</v>
+        <v>6.425730215459874</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1187814578892134</v>
+        <v>0.1185644500441157</v>
       </c>
       <c r="C34">
-        <v>1323.994877335052</v>
+        <v>1311.339063412744</v>
       </c>
       <c r="D34">
-        <v>1813.147197335052</v>
+        <v>1817.902393412744</v>
       </c>
       <c r="E34">
-        <v>557.1513200000001</v>
+        <v>574.56233</v>
       </c>
       <c r="F34">
-        <v>557.15232</v>
+        <v>574.56333</v>
       </c>
       <c r="G34">
         <v>68</v>
@@ -4075,28 +4075,28 @@
         <v>194.4</v>
       </c>
       <c r="M34">
-        <v>30.253370976</v>
+        <v>31.198788819</v>
       </c>
       <c r="N34">
-        <v>164.146629024</v>
+        <v>163.201211181</v>
       </c>
       <c r="O34">
-        <v>36.9329915304</v>
+        <v>36.72027251572501</v>
       </c>
       <c r="P34">
-        <v>127.2136374936</v>
+        <v>126.480938665275</v>
       </c>
       <c r="Q34">
-        <v>137.0136374936</v>
+        <v>136.280938665275</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1548750851311962</v>
+        <v>0.1562346642449488</v>
       </c>
       <c r="T34">
-        <v>0.7605197652422176</v>
+        <v>0.7699993525116259</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.425730215459874</v>
+        <v>6.231011118021698</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1185644500441157</v>
+        <v>0.1186109421990179</v>
       </c>
       <c r="C35">
-        <v>1311.339063412744</v>
+        <v>1292.907193338267</v>
       </c>
       <c r="D35">
-        <v>1817.902393412744</v>
+        <v>1816.881533338267</v>
       </c>
       <c r="E35">
-        <v>574.56233</v>
+        <v>591.97334</v>
       </c>
       <c r="F35">
-        <v>574.56333</v>
+        <v>591.97434</v>
       </c>
       <c r="G35">
         <v>68</v>
@@ -4157,45 +4157,45 @@
         <v>194.4</v>
       </c>
       <c r="M35">
-        <v>31.198788819</v>
+        <v>32.736181002</v>
       </c>
       <c r="N35">
-        <v>163.201211181</v>
+        <v>161.663818998</v>
       </c>
       <c r="O35">
-        <v>36.72027251572501</v>
+        <v>36.37435927455</v>
       </c>
       <c r="P35">
-        <v>126.480938665275</v>
+        <v>125.28945972345</v>
       </c>
       <c r="Q35">
-        <v>136.280938665275</v>
+        <v>135.08945972345</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1562346642449488</v>
+        <v>0.1576354427257847</v>
       </c>
       <c r="T35">
-        <v>0.7699993525116259</v>
+        <v>0.779766200001319</v>
       </c>
       <c r="U35">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.225</v>
       </c>
       <c r="W35">
-        <v>0.0420825</v>
+        <v>0.0428575</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>6.231011118021698</v>
+        <v>5.938383588119923</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1186109421990179</v>
+        <v>0.1184016843539201</v>
       </c>
       <c r="C36">
-        <v>1292.907193338267</v>
+        <v>1280.100057308958</v>
       </c>
       <c r="D36">
-        <v>1816.881533338267</v>
+        <v>1821.485407308958</v>
       </c>
       <c r="E36">
-        <v>591.97334</v>
+        <v>609.38435</v>
       </c>
       <c r="F36">
-        <v>591.97434</v>
+        <v>609.38535</v>
       </c>
       <c r="G36">
         <v>68</v>
@@ -4239,28 +4239,28 @@
         <v>194.4</v>
       </c>
       <c r="M36">
-        <v>32.736181002</v>
+        <v>33.699009855</v>
       </c>
       <c r="N36">
-        <v>161.663818998</v>
+        <v>160.700990145</v>
       </c>
       <c r="O36">
-        <v>36.37435927455</v>
+        <v>36.157722782625</v>
       </c>
       <c r="P36">
-        <v>125.28945972345</v>
+        <v>124.543267362375</v>
       </c>
       <c r="Q36">
-        <v>135.08945972345</v>
+        <v>134.343267362375</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1576354427257847</v>
+        <v>0.1590793220829541</v>
       </c>
       <c r="T36">
-        <v>0.779766200001319</v>
+        <v>0.7898335658753105</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.938383588119923</v>
+        <v>5.76871548560221</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1184016843539201</v>
+        <v>0.1181924265088224</v>
       </c>
       <c r="C37">
-        <v>1280.100057308958</v>
+        <v>1267.316312458621</v>
       </c>
       <c r="D37">
-        <v>1821.485407308958</v>
+        <v>1826.112672458621</v>
       </c>
       <c r="E37">
-        <v>609.38435</v>
+        <v>626.7953600000001</v>
       </c>
       <c r="F37">
-        <v>609.38535</v>
+        <v>626.79636</v>
       </c>
       <c r="G37">
         <v>68</v>
@@ -4321,28 +4321,28 @@
         <v>194.4</v>
       </c>
       <c r="M37">
-        <v>33.699009855</v>
+        <v>34.661838708</v>
       </c>
       <c r="N37">
-        <v>160.700990145</v>
+        <v>159.738161292</v>
       </c>
       <c r="O37">
-        <v>36.157722782625</v>
+        <v>35.9410862907</v>
       </c>
       <c r="P37">
-        <v>124.543267362375</v>
+        <v>123.7970750013</v>
       </c>
       <c r="Q37">
-        <v>134.343267362375</v>
+        <v>133.5970750013</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1590793220829541</v>
+        <v>0.160568322670035</v>
       </c>
       <c r="T37">
-        <v>0.7898335658753105</v>
+        <v>0.8002155369328642</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.76871548560221</v>
+        <v>5.608473388779927</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1181924265088224</v>
+        <v>0.1179831686637246</v>
       </c>
       <c r="C38">
-        <v>1267.31631245862</v>
+        <v>1254.556137508726</v>
       </c>
       <c r="D38">
-        <v>1826.11267245862</v>
+        <v>1830.763507508726</v>
       </c>
       <c r="E38">
-        <v>626.79536</v>
+        <v>644.20637</v>
       </c>
       <c r="F38">
-        <v>626.7963599999999</v>
+        <v>644.20737</v>
       </c>
       <c r="G38">
         <v>68</v>
@@ -4403,28 +4403,28 @@
         <v>194.4</v>
       </c>
       <c r="M38">
-        <v>34.661838708</v>
+        <v>35.624667561</v>
       </c>
       <c r="N38">
-        <v>159.738161292</v>
+        <v>158.775332439</v>
       </c>
       <c r="O38">
-        <v>35.9410862907</v>
+        <v>35.72444979877501</v>
       </c>
       <c r="P38">
-        <v>123.7970750013</v>
+        <v>123.050882640225</v>
       </c>
       <c r="Q38">
-        <v>133.5970750013</v>
+        <v>132.850882640225</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.160568322670035</v>
+        <v>0.1621045931170232</v>
       </c>
       <c r="T38">
-        <v>0.8002155369328642</v>
+        <v>0.8109270943731974</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.608473388779927</v>
+        <v>5.456893026921009</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1179831686637246</v>
+        <v>0.1177739108186268</v>
       </c>
       <c r="C39">
-        <v>1254.556137508726</v>
+        <v>1241.819713006105</v>
       </c>
       <c r="D39">
-        <v>1830.763507508726</v>
+        <v>1835.438093006105</v>
       </c>
       <c r="E39">
-        <v>644.20637</v>
+        <v>661.61738</v>
       </c>
       <c r="F39">
-        <v>644.20737</v>
+        <v>661.61838</v>
       </c>
       <c r="G39">
         <v>68</v>
@@ -4485,28 +4485,28 @@
         <v>194.4</v>
       </c>
       <c r="M39">
-        <v>35.624667561</v>
+        <v>36.587496414</v>
       </c>
       <c r="N39">
-        <v>158.775332439</v>
+        <v>157.812503586</v>
       </c>
       <c r="O39">
-        <v>35.72444979877501</v>
+        <v>35.50781330685</v>
       </c>
       <c r="P39">
-        <v>123.050882640225</v>
+        <v>122.30469027915</v>
       </c>
       <c r="Q39">
-        <v>132.850882640225</v>
+        <v>132.10469027915</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1621045931170232</v>
+        <v>0.1636904206752046</v>
       </c>
       <c r="T39">
-        <v>0.8109270943731974</v>
+        <v>0.8219841859245091</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.456893026921009</v>
+        <v>5.313290578844141</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1177739108186268</v>
+        <v>0.1175646529735291</v>
       </c>
       <c r="C40">
-        <v>1241.819713006105</v>
+        <v>1229.107221346302</v>
       </c>
       <c r="D40">
-        <v>1835.438093006105</v>
+        <v>1840.136611346302</v>
       </c>
       <c r="E40">
-        <v>661.61738</v>
+        <v>679.0283900000001</v>
       </c>
       <c r="F40">
-        <v>661.61838</v>
+        <v>679.02939</v>
       </c>
       <c r="G40">
         <v>68</v>
@@ -4567,28 +4567,28 @@
         <v>194.4</v>
       </c>
       <c r="M40">
-        <v>36.587496414</v>
+        <v>37.55032526700001</v>
       </c>
       <c r="N40">
-        <v>157.812503586</v>
+        <v>156.849674733</v>
       </c>
       <c r="O40">
-        <v>35.50781330685</v>
+        <v>35.291176814925</v>
       </c>
       <c r="P40">
-        <v>122.30469027915</v>
+        <v>121.558497918075</v>
       </c>
       <c r="Q40">
-        <v>132.10469027915</v>
+        <v>131.358497918075</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1636904206752046</v>
+        <v>0.1653282425795558</v>
       </c>
       <c r="T40">
-        <v>0.8219841859245091</v>
+        <v>0.833403805067667</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.313290578844141</v>
+        <v>5.177052358873778</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1175646529735291</v>
+        <v>0.1173553951284313</v>
       </c>
       <c r="C41">
-        <v>1229.107221346302</v>
+        <v>1216.418846797309</v>
       </c>
       <c r="D41">
-        <v>1840.136611346302</v>
+        <v>1844.859246797309</v>
       </c>
       <c r="E41">
-        <v>679.0283900000001</v>
+        <v>696.4394</v>
       </c>
       <c r="F41">
-        <v>679.02939</v>
+        <v>696.4404</v>
       </c>
       <c r="G41">
         <v>68</v>
@@ -4649,28 +4649,28 @@
         <v>194.4</v>
       </c>
       <c r="M41">
-        <v>37.55032526700001</v>
+        <v>38.51315412</v>
       </c>
       <c r="N41">
-        <v>156.849674733</v>
+        <v>155.88684588</v>
       </c>
       <c r="O41">
-        <v>35.291176814925</v>
+        <v>35.074540323</v>
       </c>
       <c r="P41">
-        <v>121.558497918075</v>
+        <v>120.812305557</v>
       </c>
       <c r="Q41">
-        <v>131.358497918075</v>
+        <v>130.612305557</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1653282425795558</v>
+        <v>0.1670206585473855</v>
       </c>
       <c r="T41">
-        <v>0.833403805067667</v>
+        <v>0.8452040781822634</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.177052358873778</v>
+        <v>5.047626049901935</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1173553951284313</v>
+        <v>0.1171461372833335</v>
       </c>
       <c r="C42">
-        <v>1216.418846797309</v>
+        <v>1203.754775523649</v>
       </c>
       <c r="D42">
-        <v>1844.859246797309</v>
+        <v>1849.606185523649</v>
       </c>
       <c r="E42">
-        <v>696.4394</v>
+        <v>713.85041</v>
       </c>
       <c r="F42">
-        <v>696.4404</v>
+        <v>713.85141</v>
       </c>
       <c r="G42">
         <v>68</v>
@@ -4731,28 +4731,28 @@
         <v>194.4</v>
       </c>
       <c r="M42">
-        <v>38.51315412</v>
+        <v>39.475982973</v>
       </c>
       <c r="N42">
-        <v>155.88684588</v>
+        <v>154.924017027</v>
       </c>
       <c r="O42">
-        <v>35.074540323</v>
+        <v>34.857903831075</v>
       </c>
       <c r="P42">
-        <v>120.812305557</v>
+        <v>120.066113195925</v>
       </c>
       <c r="Q42">
-        <v>130.612305557</v>
+        <v>129.866113195925</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1670206585473855</v>
+        <v>0.1687704445480229</v>
       </c>
       <c r="T42">
-        <v>0.8452040781822634</v>
+        <v>0.857404360554982</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.047626049901935</v>
+        <v>4.924513219416521</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1171461372833335</v>
+        <v>0.1169368794382358</v>
       </c>
       <c r="C43">
-        <v>1203.754775523649</v>
+        <v>1191.115195610839</v>
       </c>
       <c r="D43">
-        <v>1849.606185523649</v>
+        <v>1854.377615610839</v>
       </c>
       <c r="E43">
-        <v>713.85041</v>
+        <v>731.26142</v>
       </c>
       <c r="F43">
-        <v>713.85141</v>
+        <v>731.26242</v>
       </c>
       <c r="G43">
         <v>68</v>
@@ -4813,28 +4813,28 @@
         <v>194.4</v>
       </c>
       <c r="M43">
-        <v>39.475982973</v>
+        <v>40.43881182600001</v>
       </c>
       <c r="N43">
-        <v>154.924017027</v>
+        <v>153.961188174</v>
       </c>
       <c r="O43">
-        <v>34.857903831075</v>
+        <v>34.64126733915</v>
       </c>
       <c r="P43">
-        <v>120.066113195925</v>
+        <v>119.31992083485</v>
       </c>
       <c r="Q43">
-        <v>129.866113195925</v>
+        <v>129.11992083485</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1687704445480229</v>
+        <v>0.1705805679969582</v>
       </c>
       <c r="T43">
-        <v>0.857404360554982</v>
+        <v>0.8700253423198632</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.924513219416521</v>
+        <v>4.807262904668509</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1169368794382357</v>
+        <v>0.116727621593138</v>
       </c>
       <c r="C44">
-        <v>1191.11519561084</v>
+        <v>1178.500297090236</v>
       </c>
       <c r="D44">
-        <v>1854.377615610839</v>
+        <v>1859.173727090237</v>
       </c>
       <c r="E44">
-        <v>731.2614199999999</v>
+        <v>748.67243</v>
       </c>
       <c r="F44">
-        <v>731.2624199999999</v>
+        <v>748.6734299999999</v>
       </c>
       <c r="G44">
         <v>68</v>
@@ -4895,28 +4895,28 @@
         <v>194.4</v>
       </c>
       <c r="M44">
-        <v>40.438811826</v>
+        <v>41.401640679</v>
       </c>
       <c r="N44">
-        <v>153.961188174</v>
+        <v>152.998359321</v>
       </c>
       <c r="O44">
-        <v>34.64126733915</v>
+        <v>34.424630847225</v>
       </c>
       <c r="P44">
-        <v>119.31992083485</v>
+        <v>118.573728473775</v>
       </c>
       <c r="Q44">
-        <v>129.11992083485</v>
+        <v>128.373728473775</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1705805679969582</v>
+        <v>0.1724542045493649</v>
       </c>
       <c r="T44">
-        <v>0.8700253423198631</v>
+        <v>0.8830891655501787</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.807262904668509</v>
+        <v>4.695466092932032</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.116727621593138</v>
+        <v>0.1165183637480402</v>
       </c>
       <c r="C45">
-        <v>1178.500297090236</v>
+        <v>1165.910271964259</v>
       </c>
       <c r="D45">
-        <v>1859.173727090237</v>
+        <v>1863.994711964259</v>
       </c>
       <c r="E45">
-        <v>748.67243</v>
+        <v>766.08344</v>
       </c>
       <c r="F45">
-        <v>748.6734299999999</v>
+        <v>766.08444</v>
       </c>
       <c r="G45">
         <v>68</v>
@@ -4977,28 +4977,28 @@
         <v>194.4</v>
       </c>
       <c r="M45">
-        <v>41.401640679</v>
+        <v>42.364469532</v>
       </c>
       <c r="N45">
-        <v>152.998359321</v>
+        <v>152.035530468</v>
       </c>
       <c r="O45">
-        <v>34.424630847225</v>
+        <v>34.2079943553</v>
       </c>
       <c r="P45">
-        <v>118.573728473775</v>
+        <v>117.8275361127</v>
       </c>
       <c r="Q45">
-        <v>128.373728473775</v>
+        <v>127.6275361127</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1724542045493649</v>
+        <v>0.1743947566929289</v>
       </c>
       <c r="T45">
-        <v>0.8830891655501787</v>
+        <v>0.8966195538958627</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.695466092932032</v>
+        <v>4.588750954456303</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1165183637480402</v>
+        <v>0.1171809809029424</v>
       </c>
       <c r="C46">
-        <v>1165.910271964259</v>
+        <v>1133.318626168164</v>
       </c>
       <c r="D46">
-        <v>1863.994711964259</v>
+        <v>1848.814076168164</v>
       </c>
       <c r="E46">
-        <v>766.08344</v>
+        <v>783.49445</v>
       </c>
       <c r="F46">
-        <v>766.08444</v>
+        <v>783.49545</v>
       </c>
       <c r="G46">
         <v>68</v>
@@ -5059,45 +5059,45 @@
         <v>194.4</v>
       </c>
       <c r="M46">
-        <v>42.364469532</v>
+        <v>45.28603701</v>
       </c>
       <c r="N46">
-        <v>152.035530468</v>
+        <v>149.11396299</v>
       </c>
       <c r="O46">
-        <v>34.2079943553</v>
+        <v>33.55064167275</v>
       </c>
       <c r="P46">
-        <v>117.8275361127</v>
+        <v>115.56332131725</v>
       </c>
       <c r="Q46">
-        <v>127.6275361127</v>
+        <v>125.36332131725</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1743947566929289</v>
+        <v>0.1764058743689862</v>
       </c>
       <c r="T46">
-        <v>0.8966195538958627</v>
+        <v>0.9106419563632079</v>
       </c>
       <c r="U46">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V46">
         <v>0.225</v>
       </c>
       <c r="W46">
-        <v>0.0428575</v>
+        <v>0.044795</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.588750954456303</v>
+        <v>4.292713887882767</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1171809809029424</v>
+        <v>0.1169910980578447</v>
       </c>
       <c r="C47">
-        <v>1133.318626168164</v>
+        <v>1120.232518766448</v>
       </c>
       <c r="D47">
-        <v>1848.814076168164</v>
+        <v>1853.138978766448</v>
       </c>
       <c r="E47">
-        <v>783.49445</v>
+        <v>800.9054600000001</v>
       </c>
       <c r="F47">
-        <v>783.49545</v>
+        <v>800.90646</v>
       </c>
       <c r="G47">
         <v>68</v>
@@ -5141,28 +5141,28 @@
         <v>194.4</v>
       </c>
       <c r="M47">
-        <v>45.28603701</v>
+        <v>46.29239338800001</v>
       </c>
       <c r="N47">
-        <v>149.11396299</v>
+        <v>148.107606612</v>
       </c>
       <c r="O47">
-        <v>33.55064167275</v>
+        <v>33.3242114877</v>
       </c>
       <c r="P47">
-        <v>115.56332131725</v>
+        <v>114.7833951243</v>
       </c>
       <c r="Q47">
-        <v>125.36332131725</v>
+        <v>124.5833951243</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1764058743689862</v>
+        <v>0.1784914778848976</v>
       </c>
       <c r="T47">
-        <v>0.9106419563632079</v>
+        <v>0.9251837070700845</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.292713887882767</v>
+        <v>4.19939402075488</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1169910980578447</v>
+        <v>0.1168012152127469</v>
       </c>
       <c r="C48">
-        <v>1120.232518766448</v>
+        <v>1107.166693167145</v>
       </c>
       <c r="D48">
-        <v>1853.138978766448</v>
+        <v>1857.484163167145</v>
       </c>
       <c r="E48">
-        <v>800.9054600000001</v>
+        <v>818.31647</v>
       </c>
       <c r="F48">
-        <v>800.90646</v>
+        <v>818.31747</v>
       </c>
       <c r="G48">
         <v>68</v>
@@ -5223,28 +5223,28 @@
         <v>194.4</v>
       </c>
       <c r="M48">
-        <v>46.29239338800001</v>
+        <v>47.298749766</v>
       </c>
       <c r="N48">
-        <v>148.107606612</v>
+        <v>147.101250234</v>
       </c>
       <c r="O48">
-        <v>33.3242114877</v>
+        <v>33.09778130265001</v>
       </c>
       <c r="P48">
-        <v>114.7833951243</v>
+        <v>114.00346893135</v>
       </c>
       <c r="Q48">
-        <v>124.5833951243</v>
+        <v>123.80346893135</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1784914778848976</v>
+        <v>0.1806557834202772</v>
       </c>
       <c r="T48">
-        <v>0.9251837070700845</v>
+        <v>0.9402742030866545</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.19939402075488</v>
+        <v>4.11004521180265</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1168012152127469</v>
+        <v>0.1166113323676491</v>
       </c>
       <c r="C49">
-        <v>1107.166693167145</v>
+        <v>1094.121292374041</v>
       </c>
       <c r="D49">
-        <v>1857.484163167145</v>
+        <v>1861.849772374041</v>
       </c>
       <c r="E49">
-        <v>818.31647</v>
+        <v>835.72748</v>
       </c>
       <c r="F49">
-        <v>818.31747</v>
+        <v>835.72848</v>
       </c>
       <c r="G49">
         <v>68</v>
@@ -5305,28 +5305,28 @@
         <v>194.4</v>
       </c>
       <c r="M49">
-        <v>47.298749766</v>
+        <v>48.305106144</v>
       </c>
       <c r="N49">
-        <v>147.101250234</v>
+        <v>146.094893856</v>
       </c>
       <c r="O49">
-        <v>33.09778130265001</v>
+        <v>32.8713511176</v>
       </c>
       <c r="P49">
-        <v>114.00346893135</v>
+        <v>113.2235427384</v>
       </c>
       <c r="Q49">
-        <v>123.80346893135</v>
+        <v>123.0235427384</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1806557834202772</v>
+        <v>0.1829033314762483</v>
       </c>
       <c r="T49">
-        <v>0.9402742030866545</v>
+        <v>0.9559451027961695</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.11004521180265</v>
+        <v>4.024419269890094</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1166113323676491</v>
+        <v>0.1177505745225514</v>
       </c>
       <c r="C50">
-        <v>1094.121292374041</v>
+        <v>1050.821389622442</v>
       </c>
       <c r="D50">
-        <v>1861.849772374041</v>
+        <v>1835.960879622442</v>
       </c>
       <c r="E50">
-        <v>835.7274799999999</v>
+        <v>853.1384899999999</v>
       </c>
       <c r="F50">
-        <v>835.7284799999999</v>
+        <v>853.1394899999999</v>
       </c>
       <c r="G50">
         <v>68</v>
@@ -5387,45 +5387,45 @@
         <v>194.4</v>
       </c>
       <c r="M50">
-        <v>48.305106144</v>
+        <v>52.29745073699999</v>
       </c>
       <c r="N50">
-        <v>146.094893856</v>
+        <v>142.102549263</v>
       </c>
       <c r="O50">
-        <v>32.8713511176</v>
+        <v>31.973073584175</v>
       </c>
       <c r="P50">
-        <v>113.2235427384</v>
+        <v>110.129475678825</v>
       </c>
       <c r="Q50">
-        <v>123.0235427384</v>
+        <v>119.929475678825</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1829033314762483</v>
+        <v>0.1852390186716693</v>
       </c>
       <c r="T50">
-        <v>0.9559451027961695</v>
+        <v>0.9722305475923322</v>
       </c>
       <c r="U50">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V50">
         <v>0.225</v>
       </c>
       <c r="W50">
-        <v>0.044795</v>
+        <v>0.0475075</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.024419269890094</v>
+        <v>3.71719839610583</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1177505745225514</v>
+        <v>0.1175878166774536</v>
       </c>
       <c r="C51">
-        <v>1050.821389622442</v>
+        <v>1037.06482726679</v>
       </c>
       <c r="D51">
-        <v>1835.960879622442</v>
+        <v>1839.61532726679</v>
       </c>
       <c r="E51">
-        <v>853.1384899999999</v>
+        <v>870.5495</v>
       </c>
       <c r="F51">
-        <v>853.1394899999999</v>
+        <v>870.5504999999999</v>
       </c>
       <c r="G51">
         <v>68</v>
@@ -5469,28 +5469,28 @@
         <v>194.4</v>
       </c>
       <c r="M51">
-        <v>52.29745073699999</v>
+        <v>53.36474565</v>
       </c>
       <c r="N51">
-        <v>142.102549263</v>
+        <v>141.03525435</v>
       </c>
       <c r="O51">
-        <v>31.973073584175</v>
+        <v>31.73293222875</v>
       </c>
       <c r="P51">
-        <v>110.129475678825</v>
+        <v>109.30232212125</v>
       </c>
       <c r="Q51">
-        <v>119.929475678825</v>
+        <v>119.10232212125</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1852390186716693</v>
+        <v>0.1876681333549072</v>
       </c>
       <c r="T51">
-        <v>0.9722305475923322</v>
+        <v>0.9891674101803413</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.71719839610583</v>
+        <v>3.642854428183713</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1175878166774536</v>
+        <v>0.1174250588323558</v>
       </c>
       <c r="C52">
-        <v>1037.06482726679</v>
+        <v>1023.322842153626</v>
       </c>
       <c r="D52">
-        <v>1839.61532726679</v>
+        <v>1843.284352153626</v>
       </c>
       <c r="E52">
-        <v>870.5495</v>
+        <v>887.96051</v>
       </c>
       <c r="F52">
-        <v>870.5504999999999</v>
+        <v>887.96151</v>
       </c>
       <c r="G52">
         <v>68</v>
@@ -5551,28 +5551,28 @@
         <v>194.4</v>
       </c>
       <c r="M52">
-        <v>53.36474565</v>
+        <v>54.432040563</v>
       </c>
       <c r="N52">
-        <v>141.03525435</v>
+        <v>139.967959437</v>
       </c>
       <c r="O52">
-        <v>31.73293222875</v>
+        <v>31.492790873325</v>
       </c>
       <c r="P52">
-        <v>109.30232212125</v>
+        <v>108.475168563675</v>
       </c>
       <c r="Q52">
-        <v>119.10232212125</v>
+        <v>118.275168563675</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1876681333549072</v>
+        <v>0.1901963955762364</v>
       </c>
       <c r="T52">
-        <v>0.9891674101803413</v>
+        <v>1.006795573282147</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.642854428183713</v>
+        <v>3.571425909984031</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1174250588323558</v>
+        <v>0.1172623009872581</v>
       </c>
       <c r="C53">
-        <v>1023.322842153626</v>
+        <v>1009.595521678096</v>
       </c>
       <c r="D53">
-        <v>1843.284352153626</v>
+        <v>1846.968041678096</v>
       </c>
       <c r="E53">
-        <v>887.96051</v>
+        <v>905.37152</v>
       </c>
       <c r="F53">
-        <v>887.96151</v>
+        <v>905.37252</v>
       </c>
       <c r="G53">
         <v>68</v>
@@ -5633,28 +5633,28 @@
         <v>194.4</v>
       </c>
       <c r="M53">
-        <v>54.432040563</v>
+        <v>55.499335476</v>
       </c>
       <c r="N53">
-        <v>139.967959437</v>
+        <v>138.900664524</v>
       </c>
       <c r="O53">
-        <v>31.492790873325</v>
+        <v>31.2526495179</v>
       </c>
       <c r="P53">
-        <v>108.475168563675</v>
+        <v>107.6480150061</v>
       </c>
       <c r="Q53">
-        <v>118.275168563675</v>
+        <v>117.4480150061</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1901963955762364</v>
+        <v>0.1928300020567876</v>
       </c>
       <c r="T53">
-        <v>1.006795573282147</v>
+        <v>1.025158243179861</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.571425909984031</v>
+        <v>3.502744642484339</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1172623009872581</v>
+        <v>0.1182496431421603</v>
       </c>
       <c r="C54">
-        <v>1009.595521678096</v>
+        <v>970.0615920137208</v>
       </c>
       <c r="D54">
-        <v>1846.968041678096</v>
+        <v>1824.845122013721</v>
       </c>
       <c r="E54">
-        <v>905.37152</v>
+        <v>922.7825300000001</v>
       </c>
       <c r="F54">
-        <v>905.37252</v>
+        <v>922.78353</v>
       </c>
       <c r="G54">
         <v>68</v>
@@ -5715,45 +5715,45 @@
         <v>194.4</v>
       </c>
       <c r="M54">
-        <v>55.499335476</v>
+        <v>59.15042427300001</v>
       </c>
       <c r="N54">
-        <v>138.900664524</v>
+        <v>135.249575727</v>
       </c>
       <c r="O54">
-        <v>31.2526495179</v>
+        <v>30.431154538575</v>
       </c>
       <c r="P54">
-        <v>107.6480150061</v>
+        <v>104.818421188425</v>
       </c>
       <c r="Q54">
-        <v>117.4480150061</v>
+        <v>114.618421188425</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1928300020567876</v>
+        <v>0.1955756768982134</v>
       </c>
       <c r="T54">
-        <v>1.025158243179861</v>
+        <v>1.044302303285988</v>
       </c>
       <c r="U54">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V54">
         <v>0.225</v>
       </c>
       <c r="W54">
-        <v>0.0475075</v>
+        <v>0.04967750000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.502744642484339</v>
+        <v>3.286536020481876</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1182496431421603</v>
+        <v>0.1181085852970625</v>
       </c>
       <c r="C55">
-        <v>970.0615920137208</v>
+        <v>955.7786952016311</v>
       </c>
       <c r="D55">
-        <v>1824.845122013721</v>
+        <v>1827.973235201631</v>
       </c>
       <c r="E55">
-        <v>922.7825300000001</v>
+        <v>940.19354</v>
       </c>
       <c r="F55">
-        <v>922.78353</v>
+        <v>940.19454</v>
       </c>
       <c r="G55">
         <v>68</v>
@@ -5797,28 +5797,28 @@
         <v>194.4</v>
       </c>
       <c r="M55">
-        <v>59.15042427300001</v>
+        <v>60.266470014</v>
       </c>
       <c r="N55">
-        <v>135.249575727</v>
+        <v>134.133529986</v>
       </c>
       <c r="O55">
-        <v>30.431154538575</v>
+        <v>30.18004424685</v>
       </c>
       <c r="P55">
-        <v>104.818421188425</v>
+        <v>103.95348573915</v>
       </c>
       <c r="Q55">
-        <v>114.618421188425</v>
+        <v>113.75348573915</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1955756768982134</v>
+        <v>0.1984407289066576</v>
       </c>
       <c r="T55">
-        <v>1.044302303285988</v>
+        <v>1.064278713831512</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.286536020481876</v>
+        <v>3.225674242324805</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1181085852970625</v>
+        <v>0.1179675274519648</v>
       </c>
       <c r="C56">
-        <v>955.7786952016311</v>
+        <v>941.5065411032217</v>
       </c>
       <c r="D56">
-        <v>1827.973235201631</v>
+        <v>1831.112091103222</v>
       </c>
       <c r="E56">
-        <v>940.19354</v>
+        <v>957.60455</v>
       </c>
       <c r="F56">
-        <v>940.19454</v>
+        <v>957.60555</v>
       </c>
       <c r="G56">
         <v>68</v>
@@ -5879,28 +5879,28 @@
         <v>194.4</v>
       </c>
       <c r="M56">
-        <v>60.266470014</v>
+        <v>61.38251575500001</v>
       </c>
       <c r="N56">
-        <v>134.133529986</v>
+        <v>133.017484245</v>
       </c>
       <c r="O56">
-        <v>30.18004424685</v>
+        <v>29.928933955125</v>
       </c>
       <c r="P56">
-        <v>103.95348573915</v>
+        <v>103.088550289875</v>
       </c>
       <c r="Q56">
-        <v>113.75348573915</v>
+        <v>112.888550289875</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1984407289066576</v>
+        <v>0.2014331165599217</v>
       </c>
       <c r="T56">
-        <v>1.064278713831512</v>
+        <v>1.085142964845727</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.225674242324805</v>
+        <v>3.167025619737081</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1179675274519648</v>
+        <v>0.117826469606867</v>
       </c>
       <c r="C57">
-        <v>941.5065411032217</v>
+        <v>927.2451851533824</v>
       </c>
       <c r="D57">
-        <v>1831.112091103222</v>
+        <v>1834.261745153382</v>
       </c>
       <c r="E57">
-        <v>957.60455</v>
+        <v>975.0155600000001</v>
       </c>
       <c r="F57">
-        <v>957.60555</v>
+        <v>975.01656</v>
       </c>
       <c r="G57">
         <v>68</v>
@@ -5961,28 +5961,28 @@
         <v>194.4</v>
       </c>
       <c r="M57">
-        <v>61.38251575500001</v>
+        <v>62.49856149600001</v>
       </c>
       <c r="N57">
-        <v>133.017484245</v>
+        <v>131.901438504</v>
       </c>
       <c r="O57">
-        <v>29.928933955125</v>
+        <v>29.6778236634</v>
       </c>
       <c r="P57">
-        <v>103.088550289875</v>
+        <v>102.2236148406</v>
       </c>
       <c r="Q57">
-        <v>112.888550289875</v>
+        <v>112.0236148406</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2014331165599217</v>
+        <v>0.2045615218337886</v>
       </c>
       <c r="T57">
-        <v>1.085142964845727</v>
+        <v>1.106955590906041</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.167025619737081</v>
+        <v>3.110471590813204</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.117826469606867</v>
+        <v>0.1176854117617692</v>
       </c>
       <c r="C58">
-        <v>927.2451851533824</v>
+        <v>912.994683169067</v>
       </c>
       <c r="D58">
-        <v>1834.261745153382</v>
+        <v>1837.422253169067</v>
       </c>
       <c r="E58">
-        <v>975.0155600000001</v>
+        <v>992.4265700000001</v>
       </c>
       <c r="F58">
-        <v>975.01656</v>
+        <v>992.4275700000001</v>
       </c>
       <c r="G58">
         <v>68</v>
@@ -6043,28 +6043,28 @@
         <v>194.4</v>
       </c>
       <c r="M58">
-        <v>62.49856149600001</v>
+        <v>63.61460723700001</v>
       </c>
       <c r="N58">
-        <v>131.901438504</v>
+        <v>130.785392763</v>
       </c>
       <c r="O58">
-        <v>29.6778236634</v>
+        <v>29.426713371675</v>
       </c>
       <c r="P58">
-        <v>102.2236148406</v>
+        <v>101.358679391325</v>
       </c>
       <c r="Q58">
-        <v>112.0236148406</v>
+        <v>111.158679391325</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2045615218337886</v>
+        <v>0.2078354343296958</v>
       </c>
       <c r="T58">
-        <v>1.106955590906041</v>
+        <v>1.129782757713348</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.110471590813204</v>
+        <v>3.055901913781394</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1176854117617692</v>
+        <v>0.1175443539166714</v>
       </c>
       <c r="C59">
-        <v>912.994683169067</v>
+        <v>898.755091352594</v>
       </c>
       <c r="D59">
-        <v>1837.422253169067</v>
+        <v>1840.593671352594</v>
       </c>
       <c r="E59">
-        <v>992.4265700000001</v>
+        <v>1009.83758</v>
       </c>
       <c r="F59">
-        <v>992.4275700000001</v>
+        <v>1009.83858</v>
       </c>
       <c r="G59">
         <v>68</v>
@@ -6125,28 +6125,28 @@
         <v>194.4</v>
       </c>
       <c r="M59">
-        <v>63.61460723700001</v>
+        <v>64.73065297800001</v>
       </c>
       <c r="N59">
-        <v>130.785392763</v>
+        <v>129.669347022</v>
       </c>
       <c r="O59">
-        <v>29.426713371675</v>
+        <v>29.17560307995</v>
       </c>
       <c r="P59">
-        <v>101.358679391325</v>
+        <v>100.49374394205</v>
       </c>
       <c r="Q59">
-        <v>111.158679391325</v>
+        <v>110.29374394205</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2078354343296958</v>
+        <v>0.2112652474206463</v>
       </c>
       <c r="T59">
-        <v>1.129782757713348</v>
+        <v>1.153696932463859</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.055901913781394</v>
+        <v>3.00321394975068</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1175443539166714</v>
+        <v>0.1209698460715737</v>
       </c>
       <c r="C60">
-        <v>898.7550913525938</v>
+        <v>807.2990580585483</v>
       </c>
       <c r="D60">
-        <v>1840.593671352594</v>
+        <v>1766.548648058548</v>
       </c>
       <c r="E60">
-        <v>1009.83758</v>
+        <v>1027.24859</v>
       </c>
       <c r="F60">
-        <v>1009.83858</v>
+        <v>1027.24959</v>
       </c>
       <c r="G60">
         <v>68</v>
@@ -6207,45 +6207,45 @@
         <v>194.4</v>
       </c>
       <c r="M60">
-        <v>64.73065297799999</v>
+        <v>73.85924552100001</v>
       </c>
       <c r="N60">
-        <v>129.669347022</v>
+        <v>120.540754479</v>
       </c>
       <c r="O60">
-        <v>29.17560307995</v>
+        <v>27.121669757775</v>
       </c>
       <c r="P60">
-        <v>100.49374394205</v>
+        <v>93.419084721225</v>
       </c>
       <c r="Q60">
-        <v>110.29374394205</v>
+        <v>103.219084721225</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2112652474206463</v>
+        <v>0.2148623684672528</v>
       </c>
       <c r="T60">
-        <v>1.153696932463859</v>
+        <v>1.178777652324151</v>
       </c>
       <c r="U60">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V60">
         <v>0.225</v>
       </c>
       <c r="W60">
-        <v>0.04967750000000001</v>
+        <v>0.05572250000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.00321394975068</v>
+        <v>2.632033384970434</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1209698460715737</v>
+        <v>0.1208892382264759</v>
       </c>
       <c r="C61">
-        <v>807.2990580585483</v>
+        <v>791.5619468958505</v>
       </c>
       <c r="D61">
-        <v>1766.548648058548</v>
+        <v>1768.22254689585</v>
       </c>
       <c r="E61">
-        <v>1027.24859</v>
+        <v>1044.6596</v>
       </c>
       <c r="F61">
-        <v>1027.24959</v>
+        <v>1044.6606</v>
       </c>
       <c r="G61">
         <v>68</v>
@@ -6289,28 +6289,28 @@
         <v>194.4</v>
       </c>
       <c r="M61">
-        <v>73.85924552100001</v>
+        <v>75.11109714</v>
       </c>
       <c r="N61">
-        <v>120.540754479</v>
+        <v>119.28890286</v>
       </c>
       <c r="O61">
-        <v>27.121669757775</v>
+        <v>26.8400031435</v>
       </c>
       <c r="P61">
-        <v>93.419084721225</v>
+        <v>92.44889971650001</v>
       </c>
       <c r="Q61">
-        <v>103.219084721225</v>
+        <v>102.2488997165</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2148623684672528</v>
+        <v>0.2186393455661897</v>
       </c>
       <c r="T61">
-        <v>1.178777652324151</v>
+        <v>1.205112408177458</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.632033384970434</v>
+        <v>2.588166161887593</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1208892382264759</v>
+        <v>0.1208086303813782</v>
       </c>
       <c r="C62">
-        <v>791.5619468958505</v>
+        <v>775.8280109582702</v>
       </c>
       <c r="D62">
-        <v>1768.22254689585</v>
+        <v>1769.89962095827</v>
       </c>
       <c r="E62">
-        <v>1044.6596</v>
+        <v>1062.07061</v>
       </c>
       <c r="F62">
-        <v>1044.6606</v>
+        <v>1062.07161</v>
       </c>
       <c r="G62">
         <v>68</v>
@@ -6371,28 +6371,28 @@
         <v>194.4</v>
       </c>
       <c r="M62">
-        <v>75.11109714</v>
+        <v>76.36294875900001</v>
       </c>
       <c r="N62">
-        <v>119.28890286</v>
+        <v>118.037051241</v>
       </c>
       <c r="O62">
-        <v>26.8400031435</v>
+        <v>26.558336529225</v>
       </c>
       <c r="P62">
-        <v>92.44889971650001</v>
+        <v>91.478714711775</v>
       </c>
       <c r="Q62">
-        <v>102.2488997165</v>
+        <v>101.278714711775</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2186393455661897</v>
+        <v>0.2226100137984055</v>
       </c>
       <c r="T62">
-        <v>1.205112408177458</v>
+        <v>1.232797664330935</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.588166161887593</v>
+        <v>2.545737208414026</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1208086303813782</v>
+        <v>0.1207280225362804</v>
       </c>
       <c r="C63">
-        <v>775.8280109582702</v>
+        <v>760.0972592890321</v>
       </c>
       <c r="D63">
-        <v>1769.89962095827</v>
+        <v>1771.579879289032</v>
       </c>
       <c r="E63">
-        <v>1062.07061</v>
+        <v>1079.48162</v>
       </c>
       <c r="F63">
-        <v>1062.07161</v>
+        <v>1079.48262</v>
       </c>
       <c r="G63">
         <v>68</v>
@@ -6453,28 +6453,28 @@
         <v>194.4</v>
       </c>
       <c r="M63">
-        <v>76.36294875900001</v>
+        <v>77.61480037800001</v>
       </c>
       <c r="N63">
-        <v>118.037051241</v>
+        <v>116.785199622</v>
       </c>
       <c r="O63">
-        <v>26.558336529225</v>
+        <v>26.27666991495</v>
       </c>
       <c r="P63">
-        <v>91.478714711775</v>
+        <v>90.50852970705</v>
       </c>
       <c r="Q63">
-        <v>101.278714711775</v>
+        <v>100.30852970705</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2226100137984055</v>
+        <v>0.2267896645691588</v>
       </c>
       <c r="T63">
-        <v>1.232797664330935</v>
+        <v>1.261940039229331</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.545737208414026</v>
+        <v>2.504676930858961</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1207280225362804</v>
+        <v>0.1225515896911826</v>
       </c>
       <c r="C64">
-        <v>760.0972592890321</v>
+        <v>705.4381552845866</v>
       </c>
       <c r="D64">
-        <v>1771.579879289032</v>
+        <v>1734.331785284587</v>
       </c>
       <c r="E64">
-        <v>1079.48162</v>
+        <v>1096.89263</v>
       </c>
       <c r="F64">
-        <v>1079.48262</v>
+        <v>1096.89363</v>
       </c>
       <c r="G64">
         <v>68</v>
@@ -6535,45 +6535,45 @@
         <v>194.4</v>
       </c>
       <c r="M64">
-        <v>77.61480037800001</v>
+        <v>83.14453715400001</v>
       </c>
       <c r="N64">
-        <v>116.785199622</v>
+        <v>111.255462846</v>
       </c>
       <c r="O64">
-        <v>26.27666991495</v>
+        <v>25.03247914035</v>
       </c>
       <c r="P64">
-        <v>90.50852970705</v>
+        <v>86.22298370564999</v>
       </c>
       <c r="Q64">
-        <v>100.30852970705</v>
+        <v>96.02298370564998</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2267896645691588</v>
+        <v>0.2311952424086016</v>
       </c>
       <c r="T64">
-        <v>1.261940039229331</v>
+        <v>1.292657677635749</v>
       </c>
       <c r="U64">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V64">
         <v>0.225</v>
       </c>
       <c r="W64">
-        <v>0.05572250000000001</v>
+        <v>0.05874500000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.504676930858961</v>
+        <v>2.338097085559969</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1225515896911826</v>
+        <v>0.1225012068460848</v>
       </c>
       <c r="C65">
-        <v>705.4381552845866</v>
+        <v>689.0352108563973</v>
       </c>
       <c r="D65">
-        <v>1734.331785284587</v>
+        <v>1735.339850856397</v>
       </c>
       <c r="E65">
-        <v>1096.89263</v>
+        <v>1114.30364</v>
       </c>
       <c r="F65">
-        <v>1096.89363</v>
+        <v>1114.30464</v>
       </c>
       <c r="G65">
         <v>68</v>
@@ -6617,28 +6617,28 @@
         <v>194.4</v>
       </c>
       <c r="M65">
-        <v>83.14453715400001</v>
+        <v>84.464291712</v>
       </c>
       <c r="N65">
-        <v>111.255462846</v>
+        <v>109.935708288</v>
       </c>
       <c r="O65">
-        <v>25.03247914035</v>
+        <v>24.7355343648</v>
       </c>
       <c r="P65">
-        <v>86.22298370564999</v>
+        <v>85.2001739232</v>
       </c>
       <c r="Q65">
-        <v>96.02298370564998</v>
+        <v>95.00017392319998</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2311952424086016</v>
+        <v>0.2358455745724579</v>
       </c>
       <c r="T65">
-        <v>1.292657677635749</v>
+        <v>1.32508185150919</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.338097085559969</v>
+        <v>2.301564318598095</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1225012068460848</v>
+        <v>0.122450824000987</v>
       </c>
       <c r="C66">
-        <v>689.0352108563973</v>
+        <v>672.6334389687868</v>
       </c>
       <c r="D66">
-        <v>1735.339850856397</v>
+        <v>1736.349088968787</v>
       </c>
       <c r="E66">
-        <v>1114.30364</v>
+        <v>1131.71465</v>
       </c>
       <c r="F66">
-        <v>1114.30464</v>
+        <v>1131.71565</v>
       </c>
       <c r="G66">
         <v>68</v>
@@ -6699,28 +6699,28 @@
         <v>194.4</v>
       </c>
       <c r="M66">
-        <v>84.464291712</v>
+        <v>85.78404626999999</v>
       </c>
       <c r="N66">
-        <v>109.935708288</v>
+        <v>108.61595373</v>
       </c>
       <c r="O66">
-        <v>24.7355343648</v>
+        <v>24.43858958925</v>
       </c>
       <c r="P66">
-        <v>85.2001739232</v>
+        <v>84.17736414075002</v>
       </c>
       <c r="Q66">
-        <v>95.00017392319998</v>
+        <v>93.97736414075</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2358455745724579</v>
+        <v>0.2407616400028201</v>
       </c>
       <c r="T66">
-        <v>1.32508185150919</v>
+        <v>1.359358835318256</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.301564318598095</v>
+        <v>2.266155636773509</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.122450824000987</v>
+        <v>0.1224004411558893</v>
       </c>
       <c r="C67">
-        <v>672.6334389687868</v>
+        <v>656.2328416687185</v>
       </c>
       <c r="D67">
-        <v>1736.349088968787</v>
+        <v>1737.359501668718</v>
       </c>
       <c r="E67">
-        <v>1131.71465</v>
+        <v>1149.12566</v>
       </c>
       <c r="F67">
-        <v>1131.71565</v>
+        <v>1149.12666</v>
       </c>
       <c r="G67">
         <v>68</v>
@@ -6781,28 +6781,28 @@
         <v>194.4</v>
       </c>
       <c r="M67">
-        <v>85.78404626999999</v>
+        <v>87.103800828</v>
       </c>
       <c r="N67">
-        <v>108.61595373</v>
+        <v>107.296199172</v>
       </c>
       <c r="O67">
-        <v>24.43858958925</v>
+        <v>24.1416448137</v>
       </c>
       <c r="P67">
-        <v>84.17736414075002</v>
+        <v>83.1545543583</v>
       </c>
       <c r="Q67">
-        <v>93.97736414075</v>
+        <v>92.95455435829999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2407616400028201</v>
+        <v>0.2459668857526156</v>
       </c>
       <c r="T67">
-        <v>1.359358835318256</v>
+        <v>1.395652112292561</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.266155636773509</v>
+        <v>2.231819945307244</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1224004411558893</v>
+        <v>0.1223500583107915</v>
       </c>
       <c r="C68">
-        <v>656.2328416687185</v>
+        <v>639.8334210079297</v>
       </c>
       <c r="D68">
-        <v>1737.359501668718</v>
+        <v>1738.37109100793</v>
       </c>
       <c r="E68">
-        <v>1149.12566</v>
+        <v>1166.53667</v>
       </c>
       <c r="F68">
-        <v>1149.12666</v>
+        <v>1166.53767</v>
       </c>
       <c r="G68">
         <v>68</v>
@@ -6863,28 +6863,28 @@
         <v>194.4</v>
       </c>
       <c r="M68">
-        <v>87.103800828</v>
+        <v>88.423555386</v>
       </c>
       <c r="N68">
-        <v>107.296199172</v>
+        <v>105.976444614</v>
       </c>
       <c r="O68">
-        <v>24.1416448137</v>
+        <v>23.84470003815</v>
       </c>
       <c r="P68">
-        <v>83.1545543583</v>
+        <v>82.13174457585001</v>
       </c>
       <c r="Q68">
-        <v>92.95455435829999</v>
+        <v>91.93174457584999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2459668857526156</v>
+        <v>0.2514876009417925</v>
       </c>
       <c r="T68">
-        <v>1.395652112292561</v>
+        <v>1.434144981810764</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.231819945307244</v>
+        <v>2.198509199854897</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1223500583107915</v>
+        <v>0.1222996754656937</v>
       </c>
       <c r="C69">
-        <v>639.8334210079297</v>
+        <v>623.4351790429362</v>
       </c>
       <c r="D69">
-        <v>1738.37109100793</v>
+        <v>1739.383859042936</v>
       </c>
       <c r="E69">
-        <v>1166.53667</v>
+        <v>1183.94768</v>
       </c>
       <c r="F69">
-        <v>1166.53767</v>
+        <v>1183.94868</v>
       </c>
       <c r="G69">
         <v>68</v>
@@ -6945,28 +6945,28 @@
         <v>194.4</v>
       </c>
       <c r="M69">
-        <v>88.423555386</v>
+        <v>89.743309944</v>
       </c>
       <c r="N69">
-        <v>105.976444614</v>
+        <v>104.656690056</v>
       </c>
       <c r="O69">
-        <v>23.84470003815</v>
+        <v>23.5477552626</v>
       </c>
       <c r="P69">
-        <v>82.13174457585001</v>
+        <v>81.1089347934</v>
       </c>
       <c r="Q69">
-        <v>91.93174457584999</v>
+        <v>90.90893479339998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2514876009417925</v>
+        <v>0.2573533608302929</v>
       </c>
       <c r="T69">
-        <v>1.434144981810764</v>
+        <v>1.475043655673854</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.198509199854897</v>
+        <v>2.166178182209972</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1222996754656937</v>
+        <v>0.122249292620596</v>
       </c>
       <c r="C70">
-        <v>623.4351790429362</v>
+        <v>607.0381178350478</v>
       </c>
       <c r="D70">
-        <v>1739.383859042936</v>
+        <v>1740.397807835048</v>
       </c>
       <c r="E70">
-        <v>1183.94768</v>
+        <v>1201.35869</v>
       </c>
       <c r="F70">
-        <v>1183.94868</v>
+        <v>1201.35969</v>
       </c>
       <c r="G70">
         <v>68</v>
@@ -7027,28 +7027,28 @@
         <v>194.4</v>
       </c>
       <c r="M70">
-        <v>89.743309944</v>
+        <v>91.063064502</v>
       </c>
       <c r="N70">
-        <v>104.656690056</v>
+        <v>103.336935498</v>
       </c>
       <c r="O70">
-        <v>23.5477552626</v>
+        <v>23.25081048705</v>
       </c>
       <c r="P70">
-        <v>81.1089347934</v>
+        <v>80.08612501095</v>
       </c>
       <c r="Q70">
-        <v>90.90893479339998</v>
+        <v>89.88612501094998</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2573533608302929</v>
+        <v>0.2635975568406322</v>
       </c>
       <c r="T70">
-        <v>1.475043655673854</v>
+        <v>1.518580953657144</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.166178182209972</v>
+        <v>2.134784295511277</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.122249292620596</v>
+        <v>0.1221989097754982</v>
       </c>
       <c r="C71">
-        <v>607.0381178350478</v>
+        <v>590.6422394503861</v>
       </c>
       <c r="D71">
-        <v>1740.397807835048</v>
+        <v>1741.412939450386</v>
       </c>
       <c r="E71">
-        <v>1201.35869</v>
+        <v>1218.7697</v>
       </c>
       <c r="F71">
-        <v>1201.35969</v>
+        <v>1218.7707</v>
       </c>
       <c r="G71">
         <v>68</v>
@@ -7109,28 +7109,28 @@
         <v>194.4</v>
       </c>
       <c r="M71">
-        <v>91.063064502</v>
+        <v>92.38281906000002</v>
       </c>
       <c r="N71">
-        <v>103.336935498</v>
+        <v>102.01718094</v>
       </c>
       <c r="O71">
-        <v>23.25081048705</v>
+        <v>22.9538657115</v>
       </c>
       <c r="P71">
-        <v>80.08612501095</v>
+        <v>79.06331522849999</v>
       </c>
       <c r="Q71">
-        <v>89.88612501094998</v>
+        <v>88.86331522849997</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2635975568406322</v>
+        <v>0.270258032584994</v>
       </c>
       <c r="T71">
-        <v>1.518580953657144</v>
+        <v>1.565020738172653</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.134784295511277</v>
+        <v>2.104287377003972</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1221989097754982</v>
+        <v>0.1221485269304004</v>
       </c>
       <c r="C72">
-        <v>590.6422394503861</v>
+        <v>574.247545959895</v>
       </c>
       <c r="D72">
-        <v>1741.412939450386</v>
+        <v>1742.429255959895</v>
       </c>
       <c r="E72">
-        <v>1218.7697</v>
+        <v>1236.18071</v>
       </c>
       <c r="F72">
-        <v>1218.7707</v>
+        <v>1236.18171</v>
       </c>
       <c r="G72">
         <v>68</v>
@@ -7191,28 +7191,28 @@
         <v>194.4</v>
       </c>
       <c r="M72">
-        <v>92.38281906000002</v>
+        <v>93.70257361800002</v>
       </c>
       <c r="N72">
-        <v>102.01718094</v>
+        <v>100.697426382</v>
       </c>
       <c r="O72">
-        <v>22.9538657115</v>
+        <v>22.65692093595</v>
       </c>
       <c r="P72">
-        <v>79.06331522849999</v>
+        <v>78.04050544604999</v>
       </c>
       <c r="Q72">
-        <v>88.86331522849997</v>
+        <v>87.84050544604997</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.270258032584994</v>
+        <v>0.2773778514841395</v>
       </c>
       <c r="T72">
-        <v>1.565020738172653</v>
+        <v>1.614663266447852</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.104287377003972</v>
+        <v>2.074649526623634</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1221485269304004</v>
+        <v>0.1220981440853027</v>
       </c>
       <c r="C73">
-        <v>574.2475459598952</v>
+        <v>557.8540394393549</v>
       </c>
       <c r="D73">
-        <v>1742.429255959895</v>
+        <v>1743.446759439355</v>
       </c>
       <c r="E73">
-        <v>1236.18071</v>
+        <v>1253.59172</v>
       </c>
       <c r="F73">
-        <v>1236.18171</v>
+        <v>1253.59272</v>
       </c>
       <c r="G73">
         <v>68</v>
@@ -7273,28 +7273,28 @@
         <v>194.4</v>
       </c>
       <c r="M73">
-        <v>93.702573618</v>
+        <v>95.022328176</v>
       </c>
       <c r="N73">
-        <v>100.697426382</v>
+        <v>99.377671824</v>
       </c>
       <c r="O73">
-        <v>22.65692093595</v>
+        <v>22.3599761604</v>
       </c>
       <c r="P73">
-        <v>78.04050544605001</v>
+        <v>77.01769566359999</v>
       </c>
       <c r="Q73">
-        <v>87.84050544604999</v>
+        <v>86.81769566359998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2773778514841393</v>
+        <v>0.2850062288760809</v>
       </c>
       <c r="T73">
-        <v>1.614663266447852</v>
+        <v>1.667851689599851</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.074649526623635</v>
+        <v>2.045834949864973</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1220981440853027</v>
+        <v>0.1220477612402049</v>
       </c>
       <c r="C74">
-        <v>557.8540394393549</v>
+        <v>541.4617219693994</v>
       </c>
       <c r="D74">
-        <v>1743.446759439355</v>
+        <v>1744.465451969399</v>
       </c>
       <c r="E74">
-        <v>1253.59172</v>
+        <v>1271.00273</v>
       </c>
       <c r="F74">
-        <v>1253.59272</v>
+        <v>1271.00373</v>
       </c>
       <c r="G74">
         <v>68</v>
@@ -7355,28 +7355,28 @@
         <v>194.4</v>
       </c>
       <c r="M74">
-        <v>95.022328176</v>
+        <v>96.342082734</v>
       </c>
       <c r="N74">
-        <v>99.377671824</v>
+        <v>98.057917266</v>
       </c>
       <c r="O74">
-        <v>22.3599761604</v>
+        <v>22.06303138485</v>
       </c>
       <c r="P74">
-        <v>77.01769566359999</v>
+        <v>75.99488588115</v>
       </c>
       <c r="Q74">
-        <v>86.81769566359998</v>
+        <v>85.79488588114998</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2850062288760809</v>
+        <v>0.2931996712600181</v>
       </c>
       <c r="T74">
-        <v>1.667851689599851</v>
+        <v>1.724979995948294</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.045834949864973</v>
+        <v>2.017809813565453</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1220477612402049</v>
+        <v>0.1301410783951071</v>
       </c>
       <c r="C75">
-        <v>541.4617219693994</v>
+        <v>374.3654204692964</v>
       </c>
       <c r="D75">
-        <v>1744.465451969399</v>
+        <v>1594.780160469296</v>
       </c>
       <c r="E75">
-        <v>1271.00273</v>
+        <v>1288.41374</v>
       </c>
       <c r="F75">
-        <v>1271.00373</v>
+        <v>1288.41474</v>
       </c>
       <c r="G75">
         <v>68</v>
@@ -7437,45 +7437,45 @@
         <v>194.4</v>
       </c>
       <c r="M75">
-        <v>96.342082734</v>
+        <v>115.9573266</v>
       </c>
       <c r="N75">
-        <v>98.057917266</v>
+        <v>78.44267340000002</v>
       </c>
       <c r="O75">
-        <v>22.06303138485</v>
+        <v>17.649601515</v>
       </c>
       <c r="P75">
-        <v>75.99488588115</v>
+        <v>60.79307188500002</v>
       </c>
       <c r="Q75">
-        <v>85.79488588114998</v>
+        <v>70.593071885</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2931996712600181</v>
+        <v>0.3020233784427197</v>
       </c>
       <c r="T75">
-        <v>1.724979995948294</v>
+        <v>1.786502787400465</v>
       </c>
       <c r="U75">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V75">
         <v>0.225</v>
       </c>
       <c r="W75">
-        <v>0.05874500000000001</v>
+        <v>0.06974999999999999</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y75">
-        <v>2.017809813565453</v>
+        <v>1.676478802159622</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1301410783951071</v>
+        <v>0.1302007455500094</v>
       </c>
       <c r="C76">
-        <v>374.3654204692964</v>
+        <v>355.9461988373537</v>
       </c>
       <c r="D76">
-        <v>1594.780160469296</v>
+        <v>1593.771948837354</v>
       </c>
       <c r="E76">
-        <v>1288.41374</v>
+        <v>1305.82475</v>
       </c>
       <c r="F76">
-        <v>1288.41474</v>
+        <v>1305.82575</v>
       </c>
       <c r="G76">
         <v>68</v>
@@ -7519,28 +7519,28 @@
         <v>194.4</v>
       </c>
       <c r="M76">
-        <v>115.9573266</v>
+        <v>117.5243175</v>
       </c>
       <c r="N76">
-        <v>78.44267340000002</v>
+        <v>76.87568250000001</v>
       </c>
       <c r="O76">
-        <v>17.649601515</v>
+        <v>17.2970285625</v>
       </c>
       <c r="P76">
-        <v>60.79307188500002</v>
+        <v>59.57865393750001</v>
       </c>
       <c r="Q76">
-        <v>70.593071885</v>
+        <v>69.37865393749999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3020233784427197</v>
+        <v>0.3115529822000374</v>
       </c>
       <c r="T76">
-        <v>1.786502787400465</v>
+        <v>1.852947402168808</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.676478802159622</v>
+        <v>1.65412575146416</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1302007455500094</v>
+        <v>0.1302604127049116</v>
       </c>
       <c r="C77">
-        <v>355.9461988373537</v>
+        <v>337.5282511722005</v>
       </c>
       <c r="D77">
-        <v>1593.771948837354</v>
+        <v>1592.765011172201</v>
       </c>
       <c r="E77">
-        <v>1305.82475</v>
+        <v>1323.23576</v>
       </c>
       <c r="F77">
-        <v>1305.82575</v>
+        <v>1323.23676</v>
       </c>
       <c r="G77">
         <v>68</v>
@@ -7601,28 +7601,28 @@
         <v>194.4</v>
       </c>
       <c r="M77">
-        <v>117.5243175</v>
+        <v>119.0913084</v>
       </c>
       <c r="N77">
-        <v>76.87568250000001</v>
+        <v>75.3086916</v>
       </c>
       <c r="O77">
-        <v>17.2970285625</v>
+        <v>16.94445561</v>
       </c>
       <c r="P77">
-        <v>59.57865393750001</v>
+        <v>58.36423599</v>
       </c>
       <c r="Q77">
-        <v>69.37865393749999</v>
+        <v>68.16423598999998</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3115529822000374</v>
+        <v>0.3218767196037983</v>
       </c>
       <c r="T77">
-        <v>1.852947402168808</v>
+        <v>1.924929068167847</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.65412575146416</v>
+        <v>1.632360938944895</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1302604127049116</v>
+        <v>0.1303200798598138</v>
       </c>
       <c r="C78">
-        <v>337.5282511722005</v>
+        <v>319.1115750607025</v>
       </c>
       <c r="D78">
-        <v>1592.765011172201</v>
+        <v>1591.759345060703</v>
       </c>
       <c r="E78">
-        <v>1323.23576</v>
+        <v>1340.64677</v>
       </c>
       <c r="F78">
-        <v>1323.23676</v>
+        <v>1340.64777</v>
       </c>
       <c r="G78">
         <v>68</v>
@@ -7683,28 +7683,28 @@
         <v>194.4</v>
       </c>
       <c r="M78">
-        <v>119.0913084</v>
+        <v>120.6582993</v>
       </c>
       <c r="N78">
-        <v>75.3086916</v>
+        <v>73.74170070000001</v>
       </c>
       <c r="O78">
-        <v>16.94445561</v>
+        <v>16.5918826575</v>
       </c>
       <c r="P78">
-        <v>58.36423599</v>
+        <v>57.14981804250001</v>
       </c>
       <c r="Q78">
-        <v>68.16423598999998</v>
+        <v>66.9498180425</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3218767196037983</v>
+        <v>0.3330981733035383</v>
       </c>
       <c r="T78">
-        <v>1.924929068167847</v>
+        <v>2.00317000947115</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.632360938944895</v>
+        <v>1.611161446231324</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1303200798598138</v>
+        <v>0.1303797470147161</v>
       </c>
       <c r="C79">
-        <v>319.1115750607025</v>
+        <v>300.6961680958166</v>
       </c>
       <c r="D79">
-        <v>1591.759345060703</v>
+        <v>1590.754948095817</v>
       </c>
       <c r="E79">
-        <v>1340.64677</v>
+        <v>1358.05778</v>
       </c>
       <c r="F79">
-        <v>1340.64777</v>
+        <v>1358.05878</v>
       </c>
       <c r="G79">
         <v>68</v>
@@ -7765,28 +7765,28 @@
         <v>194.4</v>
       </c>
       <c r="M79">
-        <v>120.6582993</v>
+        <v>122.2252902</v>
       </c>
       <c r="N79">
-        <v>73.74170070000001</v>
+        <v>72.1747098</v>
       </c>
       <c r="O79">
-        <v>16.5918826575</v>
+        <v>16.239309705</v>
       </c>
       <c r="P79">
-        <v>57.14981804250001</v>
+        <v>55.93540009500001</v>
       </c>
       <c r="Q79">
-        <v>66.9498180425</v>
+        <v>65.73540009499999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3330981733035383</v>
+        <v>0.3453397591578002</v>
       </c>
       <c r="T79">
-        <v>2.00317000947115</v>
+        <v>2.088523763620209</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.611161446231324</v>
+        <v>1.590505530254</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1303797470147161</v>
+        <v>0.1304394141696183</v>
       </c>
       <c r="C80">
-        <v>300.6961680958166</v>
+        <v>282.2820278765716</v>
       </c>
       <c r="D80">
-        <v>1590.754948095817</v>
+        <v>1589.751817876572</v>
       </c>
       <c r="E80">
-        <v>1358.05778</v>
+        <v>1375.46879</v>
       </c>
       <c r="F80">
-        <v>1358.05878</v>
+        <v>1375.46979</v>
       </c>
       <c r="G80">
         <v>68</v>
@@ -7847,28 +7847,28 @@
         <v>194.4</v>
       </c>
       <c r="M80">
-        <v>122.2252902</v>
+        <v>123.7922811</v>
       </c>
       <c r="N80">
-        <v>72.1747098</v>
+        <v>70.60771890000002</v>
       </c>
       <c r="O80">
-        <v>16.239309705</v>
+        <v>15.88673675250001</v>
       </c>
       <c r="P80">
-        <v>55.93540009500001</v>
+        <v>54.72098214750002</v>
       </c>
       <c r="Q80">
-        <v>65.73540009499999</v>
+        <v>64.52098214750001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3453397591578002</v>
+        <v>0.3587472103315156</v>
       </c>
       <c r="T80">
-        <v>2.088523763620209</v>
+        <v>2.182006446735844</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.590505530254</v>
+        <v>1.57037254885838</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1304394141696183</v>
+        <v>0.1304990813245205</v>
       </c>
       <c r="C81">
-        <v>282.2820278765716</v>
+        <v>263.8691520080467</v>
       </c>
       <c r="D81">
-        <v>1589.751817876572</v>
+        <v>1588.749952008047</v>
       </c>
       <c r="E81">
-        <v>1375.46879</v>
+        <v>1392.8798</v>
       </c>
       <c r="F81">
-        <v>1375.46979</v>
+        <v>1392.8808</v>
       </c>
       <c r="G81">
         <v>68</v>
@@ -7929,28 +7929,28 @@
         <v>194.4</v>
       </c>
       <c r="M81">
-        <v>123.7922811</v>
+        <v>125.359272</v>
       </c>
       <c r="N81">
-        <v>70.60771890000002</v>
+        <v>69.04072800000002</v>
       </c>
       <c r="O81">
-        <v>15.88673675250001</v>
+        <v>15.5341638</v>
       </c>
       <c r="P81">
-        <v>54.72098214750002</v>
+        <v>53.50656420000001</v>
       </c>
       <c r="Q81">
-        <v>64.52098214750001</v>
+        <v>63.3065642</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3587472103315156</v>
+        <v>0.3734954066226026</v>
       </c>
       <c r="T81">
-        <v>2.182006446735844</v>
+        <v>2.284837398163043</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.57037254885838</v>
+        <v>1.55074289199765</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1304990813245205</v>
+        <v>0.1305587484794227</v>
       </c>
       <c r="C82">
-        <v>263.8691520080467</v>
+        <v>245.4575381013567</v>
       </c>
       <c r="D82">
-        <v>1588.749952008047</v>
+        <v>1587.749348101357</v>
       </c>
       <c r="E82">
-        <v>1392.8798</v>
+        <v>1410.29081</v>
       </c>
       <c r="F82">
-        <v>1392.8808</v>
+        <v>1410.29181</v>
       </c>
       <c r="G82">
         <v>68</v>
@@ -8011,28 +8011,28 @@
         <v>194.4</v>
       </c>
       <c r="M82">
-        <v>125.359272</v>
+        <v>126.9262629</v>
       </c>
       <c r="N82">
-        <v>69.04072800000002</v>
+        <v>67.47373710000002</v>
       </c>
       <c r="O82">
-        <v>15.5341638</v>
+        <v>15.18159084750001</v>
       </c>
       <c r="P82">
-        <v>53.50656420000001</v>
+        <v>52.29214625250002</v>
       </c>
       <c r="Q82">
-        <v>63.3065642</v>
+        <v>62.0921462525</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3734954066226026</v>
+        <v>0.3897960446285408</v>
       </c>
       <c r="T82">
-        <v>2.284837398163043</v>
+        <v>2.398492660266788</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.55074289199765</v>
+        <v>1.53159791802237</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1305587484794227</v>
+        <v>0.130618415634325</v>
       </c>
       <c r="C83">
-        <v>245.4575381013567</v>
+        <v>227.0471837736291</v>
       </c>
       <c r="D83">
-        <v>1587.749348101357</v>
+        <v>1586.750003773629</v>
       </c>
       <c r="E83">
-        <v>1410.29081</v>
+        <v>1427.70182</v>
       </c>
       <c r="F83">
-        <v>1410.29181</v>
+        <v>1427.70282</v>
       </c>
       <c r="G83">
         <v>68</v>
@@ -8093,28 +8093,28 @@
         <v>194.4</v>
       </c>
       <c r="M83">
-        <v>126.9262629</v>
+        <v>128.4932538</v>
       </c>
       <c r="N83">
-        <v>67.47373710000002</v>
+        <v>65.90674620000001</v>
       </c>
       <c r="O83">
-        <v>15.18159084750001</v>
+        <v>14.829017895</v>
       </c>
       <c r="P83">
-        <v>52.29214625250002</v>
+        <v>51.07772830500001</v>
       </c>
       <c r="Q83">
-        <v>62.0921462525</v>
+        <v>60.87772830499999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3897960446285408</v>
+        <v>0.4079078646351388</v>
       </c>
       <c r="T83">
-        <v>2.398492660266788</v>
+        <v>2.524776284826506</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.53159791802237</v>
+        <v>1.512919894631854</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.130618415634325</v>
+        <v>0.1707559053814476</v>
       </c>
       <c r="C84">
-        <v>227.0471837736291</v>
+        <v>-262.3512816589334</v>
       </c>
       <c r="D84">
-        <v>1586.750003773629</v>
+        <v>1114.762548341067</v>
       </c>
       <c r="E84">
-        <v>1427.70182</v>
+        <v>1445.11283</v>
       </c>
       <c r="F84">
-        <v>1427.70282</v>
+        <v>1445.11383</v>
       </c>
       <c r="G84">
         <v>68</v>
@@ -8175,45 +8175,45 @@
         <v>194.4</v>
       </c>
       <c r="M84">
-        <v>128.4932538</v>
+        <v>212.142710244</v>
       </c>
       <c r="N84">
-        <v>65.90674620000001</v>
+        <v>-17.74271024400002</v>
       </c>
       <c r="O84">
-        <v>14.829017895</v>
+        <v>-3.992109804900005</v>
       </c>
       <c r="P84">
-        <v>51.07772830500001</v>
+        <v>-13.75060043910002</v>
       </c>
       <c r="Q84">
-        <v>60.87772830499999</v>
+        <v>-3.950600439100034</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4079078646351388</v>
+        <v>0.4354937660694678</v>
       </c>
       <c r="T84">
-        <v>2.524776284826506</v>
+        <v>2.717117397901013</v>
       </c>
       <c r="U84">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.225</v>
+        <v>0.2061819609530377</v>
       </c>
       <c r="W84">
-        <v>0.06974999999999999</v>
+        <v>0.1165324881320941</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y84">
-        <v>1.512919894631854</v>
+        <v>0.9163642709023897</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1707559053814476</v>
+        <v>0.1717659053814476</v>
       </c>
       <c r="C85">
-        <v>-262.3512816589334</v>
+        <v>-288.0443232982757</v>
       </c>
       <c r="D85">
-        <v>1114.762548341067</v>
+        <v>1106.480516701724</v>
       </c>
       <c r="E85">
-        <v>1445.11283</v>
+        <v>1462.52384</v>
       </c>
       <c r="F85">
-        <v>1445.11383</v>
+        <v>1462.52484</v>
       </c>
       <c r="G85">
         <v>68</v>
@@ -8257,37 +8257,37 @@
         <v>194.4</v>
       </c>
       <c r="M85">
-        <v>212.142710244</v>
+        <v>214.698646512</v>
       </c>
       <c r="N85">
-        <v>-17.74271024400002</v>
+        <v>-20.29864651200003</v>
       </c>
       <c r="O85">
-        <v>-3.992109804900005</v>
+        <v>-4.567195465200007</v>
       </c>
       <c r="P85">
-        <v>-13.75060043910002</v>
+        <v>-15.73145104680003</v>
       </c>
       <c r="Q85">
-        <v>-3.950600439100034</v>
+        <v>-5.931451046800042</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4354937660694678</v>
+        <v>0.4598496264488097</v>
       </c>
       <c r="T85">
-        <v>2.717117397901013</v>
+        <v>2.886937235269826</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2061819609530377</v>
+        <v>0.2037274137988349</v>
       </c>
       <c r="W85">
-        <v>0.1165324881320941</v>
+        <v>0.1168928156543311</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.9163642709023897</v>
+        <v>0.905455172439266</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1717659053814476</v>
+        <v>0.1727759053814476</v>
       </c>
       <c r="C86">
-        <v>-288.0443232982755</v>
+        <v>-313.6152111971553</v>
       </c>
       <c r="D86">
-        <v>1106.480516701724</v>
+        <v>1098.320638802845</v>
       </c>
       <c r="E86">
-        <v>1462.52384</v>
+        <v>1479.93485</v>
       </c>
       <c r="F86">
-        <v>1462.52484</v>
+        <v>1479.93585</v>
       </c>
       <c r="G86">
         <v>68</v>
@@ -8339,37 +8339,37 @@
         <v>194.4</v>
       </c>
       <c r="M86">
-        <v>214.698646512</v>
+        <v>217.25458278</v>
       </c>
       <c r="N86">
-        <v>-20.29864651199998</v>
+        <v>-22.85458277999999</v>
       </c>
       <c r="O86">
-        <v>-4.567195465199995</v>
+        <v>-5.142281125499998</v>
       </c>
       <c r="P86">
-        <v>-15.73145104679998</v>
+        <v>-17.71230165449999</v>
       </c>
       <c r="Q86">
-        <v>-5.931451046799999</v>
+        <v>-7.912301654500006</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4598496264488093</v>
+        <v>0.48745293487873</v>
       </c>
       <c r="T86">
-        <v>2.886937235269824</v>
+        <v>3.079399717621147</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2037274137988349</v>
+        <v>0.2013306206953192</v>
       </c>
       <c r="W86">
-        <v>0.116892815654331</v>
+        <v>0.1172446648819272</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9054551724392662</v>
+        <v>0.894802758645863</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1727759053814476</v>
+        <v>0.1737859053814476</v>
       </c>
       <c r="C87">
-        <v>-313.6152111971553</v>
+        <v>-339.0666280852099</v>
       </c>
       <c r="D87">
-        <v>1098.320638802845</v>
+        <v>1090.28023191479</v>
       </c>
       <c r="E87">
-        <v>1479.93485</v>
+        <v>1497.34586</v>
       </c>
       <c r="F87">
-        <v>1479.93585</v>
+        <v>1497.34686</v>
       </c>
       <c r="G87">
         <v>68</v>
@@ -8421,37 +8421,37 @@
         <v>194.4</v>
       </c>
       <c r="M87">
-        <v>217.25458278</v>
+        <v>219.810519048</v>
       </c>
       <c r="N87">
-        <v>-22.85458277999999</v>
+        <v>-25.410519048</v>
       </c>
       <c r="O87">
-        <v>-5.142281125499998</v>
+        <v>-5.717366785799999</v>
       </c>
       <c r="P87">
-        <v>-17.71230165449999</v>
+        <v>-19.6931522622</v>
       </c>
       <c r="Q87">
-        <v>-7.912301654500006</v>
+        <v>-9.893152262200015</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.48745293487873</v>
+        <v>0.5189995730843535</v>
       </c>
       <c r="T87">
-        <v>3.079399717621147</v>
+        <v>3.29935684030837</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2013306206953192</v>
+        <v>0.1989895669663038</v>
       </c>
       <c r="W87">
-        <v>0.1172446648819272</v>
+        <v>0.1175883315693466</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.894802758645863</v>
+        <v>0.8843980754057948</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1737859053814476</v>
+        <v>0.1747959053814476</v>
       </c>
       <c r="C88">
-        <v>-339.0666280852099</v>
+        <v>-364.4011787058253</v>
       </c>
       <c r="D88">
-        <v>1090.28023191479</v>
+        <v>1082.356691294175</v>
       </c>
       <c r="E88">
-        <v>1497.34586</v>
+        <v>1514.75687</v>
       </c>
       <c r="F88">
-        <v>1497.34686</v>
+        <v>1514.75787</v>
       </c>
       <c r="G88">
         <v>68</v>
@@ -8503,37 +8503,37 @@
         <v>194.4</v>
       </c>
       <c r="M88">
-        <v>219.810519048</v>
+        <v>222.366455316</v>
       </c>
       <c r="N88">
-        <v>-25.410519048</v>
+        <v>-27.96645531600001</v>
       </c>
       <c r="O88">
-        <v>-5.717366785799999</v>
+        <v>-6.292452446100002</v>
       </c>
       <c r="P88">
-        <v>-19.6931522622</v>
+        <v>-21.67400286990001</v>
       </c>
       <c r="Q88">
-        <v>-9.893152262200015</v>
+        <v>-11.87400286990002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5189995730843535</v>
+        <v>0.5553995402446885</v>
       </c>
       <c r="T88">
-        <v>3.29935684030837</v>
+        <v>3.553153520332092</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1989895669663038</v>
+        <v>0.1967023305643923</v>
       </c>
       <c r="W88">
-        <v>0.1175883315693466</v>
+        <v>0.1179240978731472</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8843980754057948</v>
+        <v>0.8742325802861879</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1747959053814476</v>
+        <v>0.1758059053814476</v>
       </c>
       <c r="C89">
-        <v>-364.4011787058253</v>
+        <v>-389.6213926294872</v>
       </c>
       <c r="D89">
-        <v>1082.356691294175</v>
+        <v>1074.547487370513</v>
       </c>
       <c r="E89">
-        <v>1514.75687</v>
+        <v>1532.16788</v>
       </c>
       <c r="F89">
-        <v>1514.75787</v>
+        <v>1532.16888</v>
       </c>
       <c r="G89">
         <v>68</v>
@@ -8585,37 +8585,37 @@
         <v>194.4</v>
       </c>
       <c r="M89">
-        <v>222.366455316</v>
+        <v>224.922391584</v>
       </c>
       <c r="N89">
-        <v>-27.96645531600001</v>
+        <v>-30.52239158400002</v>
       </c>
       <c r="O89">
-        <v>-6.292452446100002</v>
+        <v>-6.867538106400004</v>
       </c>
       <c r="P89">
-        <v>-21.67400286990001</v>
+        <v>-23.65485347760001</v>
       </c>
       <c r="Q89">
-        <v>-11.87400286990002</v>
+        <v>-13.85485347760003</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5553995402446885</v>
+        <v>0.5978661685984125</v>
       </c>
       <c r="T89">
-        <v>3.553153520332092</v>
+        <v>3.849249647026433</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1967023305643923</v>
+        <v>0.1944670768079788</v>
       </c>
       <c r="W89">
-        <v>0.1179240978731472</v>
+        <v>0.1182522331245887</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8742325802861879</v>
+        <v>0.8642981191465722</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1758059053814476</v>
+        <v>0.1768159053814476</v>
       </c>
       <c r="C90">
-        <v>-389.6213926294872</v>
+        <v>-414.7297269462215</v>
       </c>
       <c r="D90">
-        <v>1074.547487370513</v>
+        <v>1066.850163053778</v>
       </c>
       <c r="E90">
-        <v>1532.16788</v>
+        <v>1549.57889</v>
       </c>
       <c r="F90">
-        <v>1532.16888</v>
+        <v>1549.57989</v>
       </c>
       <c r="G90">
         <v>68</v>
@@ -8667,37 +8667,37 @@
         <v>194.4</v>
       </c>
       <c r="M90">
-        <v>224.922391584</v>
+        <v>227.478327852</v>
       </c>
       <c r="N90">
-        <v>-30.52239158400002</v>
+        <v>-33.078327852</v>
       </c>
       <c r="O90">
-        <v>-6.867538106400004</v>
+        <v>-7.442623766700001</v>
       </c>
       <c r="P90">
-        <v>-23.65485347760001</v>
+        <v>-25.6357040853</v>
       </c>
       <c r="Q90">
-        <v>-13.85485347760003</v>
+        <v>-15.83570408530002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5978661685984125</v>
+        <v>0.6480540021073592</v>
       </c>
       <c r="T90">
-        <v>3.849249647026433</v>
+        <v>4.199181433119746</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1944670768079788</v>
+        <v>0.1922820534730577</v>
       </c>
       <c r="W90">
-        <v>0.1182522331245887</v>
+        <v>0.1185729945501552</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8642981191465722</v>
+        <v>0.8545869043247006</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1768159053814476</v>
+        <v>0.1778259053814476</v>
       </c>
       <c r="C91">
-        <v>-414.7297269462215</v>
+        <v>-439.7285688431316</v>
       </c>
       <c r="D91">
-        <v>1066.850163053778</v>
+        <v>1059.262331156868</v>
       </c>
       <c r="E91">
-        <v>1549.57889</v>
+        <v>1566.9899</v>
       </c>
       <c r="F91">
-        <v>1549.57989</v>
+        <v>1566.9909</v>
       </c>
       <c r="G91">
         <v>68</v>
@@ -8749,37 +8749,37 @@
         <v>194.4</v>
       </c>
       <c r="M91">
-        <v>227.478327852</v>
+        <v>230.03426412</v>
       </c>
       <c r="N91">
-        <v>-33.078327852</v>
+        <v>-35.63426412000001</v>
       </c>
       <c r="O91">
-        <v>-7.442623766700001</v>
+        <v>-8.017709427000003</v>
       </c>
       <c r="P91">
-        <v>-25.6357040853</v>
+        <v>-27.61655469300001</v>
       </c>
       <c r="Q91">
-        <v>-15.83570408530002</v>
+        <v>-17.81655469300003</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6480540021073592</v>
+        <v>0.7082794023180952</v>
       </c>
       <c r="T91">
-        <v>4.199181433119746</v>
+        <v>4.61909957643172</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1922820534730577</v>
+        <v>0.1901455862122459</v>
       </c>
       <c r="W91">
-        <v>0.1185729945501552</v>
+        <v>0.1188866279440423</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8545869043247006</v>
+        <v>0.8450914942766483</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1778259053814476</v>
+        <v>0.1788359053814476</v>
       </c>
       <c r="C92">
-        <v>-439.7285688431316</v>
+        <v>-464.6202380727195</v>
       </c>
       <c r="D92">
-        <v>1059.262331156868</v>
+        <v>1051.781671927281</v>
       </c>
       <c r="E92">
-        <v>1566.9899</v>
+        <v>1584.40091</v>
       </c>
       <c r="F92">
-        <v>1566.9909</v>
+        <v>1584.40191</v>
       </c>
       <c r="G92">
         <v>68</v>
@@ -8831,37 +8831,37 @@
         <v>194.4</v>
       </c>
       <c r="M92">
-        <v>230.03426412</v>
+        <v>232.590200388</v>
       </c>
       <c r="N92">
-        <v>-35.63426412000001</v>
+        <v>-38.19020038800002</v>
       </c>
       <c r="O92">
-        <v>-8.017709427000003</v>
+        <v>-8.592795087300006</v>
       </c>
       <c r="P92">
-        <v>-27.61655469300001</v>
+        <v>-29.59740530070002</v>
       </c>
       <c r="Q92">
-        <v>-17.81655469300003</v>
+        <v>-19.79740530070004</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7082794023180952</v>
+        <v>0.7818882247978836</v>
       </c>
       <c r="T92">
-        <v>4.61909957643172</v>
+        <v>5.132332862701912</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1901455862122459</v>
+        <v>0.1880560742758476</v>
       </c>
       <c r="W92">
-        <v>0.1188866279440423</v>
+        <v>0.1191933682963056</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8450914942766483</v>
+        <v>0.8358047745593224</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1788359053814476</v>
+        <v>0.1798459053814476</v>
       </c>
       <c r="C93">
-        <v>-464.6202380727195</v>
+        <v>-489.4069893173501</v>
       </c>
       <c r="D93">
-        <v>1051.781671927281</v>
+        <v>1044.40593068265</v>
       </c>
       <c r="E93">
-        <v>1584.40091</v>
+        <v>1601.81192</v>
       </c>
       <c r="F93">
-        <v>1584.40191</v>
+        <v>1601.81292</v>
       </c>
       <c r="G93">
         <v>68</v>
@@ -8913,37 +8913,37 @@
         <v>194.4</v>
       </c>
       <c r="M93">
-        <v>232.590200388</v>
+        <v>235.146136656</v>
       </c>
       <c r="N93">
-        <v>-38.19020038800002</v>
+        <v>-40.74613665600003</v>
       </c>
       <c r="O93">
-        <v>-8.592795087300006</v>
+        <v>-9.167880747600007</v>
       </c>
       <c r="P93">
-        <v>-29.59740530070002</v>
+        <v>-31.57825590840002</v>
       </c>
       <c r="Q93">
-        <v>-19.79740530070004</v>
+        <v>-21.77825590840004</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7818882247978836</v>
+        <v>0.8738992528976193</v>
       </c>
       <c r="T93">
-        <v>5.132332862701912</v>
+        <v>5.773874470539653</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1880560742758476</v>
+        <v>0.1860119865119796</v>
       </c>
       <c r="W93">
-        <v>0.1191933682963056</v>
+        <v>0.1194934403800414</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8358047745593224</v>
+        <v>0.8267199400532429</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1798459053814476</v>
+        <v>0.1808559053814476</v>
       </c>
       <c r="C94">
-        <v>-489.4069893173501</v>
+        <v>-514.0910144549234</v>
       </c>
       <c r="D94">
-        <v>1044.40593068265</v>
+        <v>1037.132915545076</v>
       </c>
       <c r="E94">
-        <v>1601.81192</v>
+        <v>1619.22293</v>
       </c>
       <c r="F94">
-        <v>1601.81292</v>
+        <v>1619.22393</v>
       </c>
       <c r="G94">
         <v>68</v>
@@ -8995,37 +8995,37 @@
         <v>194.4</v>
       </c>
       <c r="M94">
-        <v>235.146136656</v>
+        <v>237.702072924</v>
       </c>
       <c r="N94">
-        <v>-40.74613665600003</v>
+        <v>-43.30207292399999</v>
       </c>
       <c r="O94">
-        <v>-9.167880747600007</v>
+        <v>-9.742966407899997</v>
       </c>
       <c r="P94">
-        <v>-31.57825590840002</v>
+        <v>-33.55910651609999</v>
       </c>
       <c r="Q94">
-        <v>-21.77825590840004</v>
+        <v>-23.7591065161</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8738992528976193</v>
+        <v>0.9921991461687077</v>
       </c>
       <c r="T94">
-        <v>5.773874470539653</v>
+        <v>6.598713680616746</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1860119865119796</v>
+        <v>0.1840118576247541</v>
       </c>
       <c r="W94">
-        <v>0.1194934403800414</v>
+        <v>0.1197870593006861</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8267199400532429</v>
+        <v>0.8178304783322404</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1808559053814476</v>
+        <v>0.1818659053814476</v>
       </c>
       <c r="C95">
-        <v>-514.0910144549234</v>
+        <v>-538.6744447305355</v>
       </c>
       <c r="D95">
-        <v>1037.132915545076</v>
+        <v>1029.960495269464</v>
       </c>
       <c r="E95">
-        <v>1619.22293</v>
+        <v>1636.63394</v>
       </c>
       <c r="F95">
-        <v>1619.22393</v>
+        <v>1636.63494</v>
       </c>
       <c r="G95">
         <v>68</v>
@@ -9077,37 +9077,37 @@
         <v>194.4</v>
       </c>
       <c r="M95">
-        <v>237.702072924</v>
+        <v>240.258009192</v>
       </c>
       <c r="N95">
-        <v>-43.30207292399999</v>
+        <v>-45.858009192</v>
       </c>
       <c r="O95">
-        <v>-9.742966407899997</v>
+        <v>-10.3180520682</v>
       </c>
       <c r="P95">
-        <v>-33.55910651609999</v>
+        <v>-35.53995712379999</v>
       </c>
       <c r="Q95">
-        <v>-23.7591065161</v>
+        <v>-25.73995712380001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9921991461687077</v>
+        <v>1.149932337196826</v>
       </c>
       <c r="T95">
-        <v>6.598713680616746</v>
+        <v>7.698499294052873</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1840118576247541</v>
+        <v>0.1820542846712993</v>
       </c>
       <c r="W95">
-        <v>0.1197870593006861</v>
+        <v>0.1200744310102533</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8178304783322404</v>
+        <v>0.8091301540946634</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1818659053814476</v>
+        <v>0.1828759053814476</v>
       </c>
       <c r="C96">
-        <v>-538.6744447305355</v>
+        <v>-563.1593528386445</v>
       </c>
       <c r="D96">
-        <v>1029.960495269464</v>
+        <v>1022.886597161355</v>
       </c>
       <c r="E96">
-        <v>1636.63394</v>
+        <v>1654.04495</v>
       </c>
       <c r="F96">
-        <v>1636.63494</v>
+        <v>1654.04595</v>
       </c>
       <c r="G96">
         <v>68</v>
@@ -9159,37 +9159,37 @@
         <v>194.4</v>
       </c>
       <c r="M96">
-        <v>240.258009192</v>
+        <v>242.81394546</v>
       </c>
       <c r="N96">
-        <v>-45.858009192</v>
+        <v>-48.41394546000001</v>
       </c>
       <c r="O96">
-        <v>-10.3180520682</v>
+        <v>-10.8931377285</v>
       </c>
       <c r="P96">
-        <v>-35.53995712379999</v>
+        <v>-37.52080773150001</v>
       </c>
       <c r="Q96">
-        <v>-25.73995712380001</v>
+        <v>-27.72080773150002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.149932337196826</v>
+        <v>1.370758804636192</v>
       </c>
       <c r="T96">
-        <v>7.698499294052873</v>
+        <v>9.238199152863453</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1820542846712993</v>
+        <v>0.1801379237800224</v>
       </c>
       <c r="W96">
-        <v>0.1200744310102533</v>
+        <v>0.1203557527890927</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8091301540946634</v>
+        <v>0.8006129945778774</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1828759053814476</v>
+        <v>0.2394041897929454</v>
       </c>
       <c r="C97">
-        <v>-563.1593528386445</v>
+        <v>-864.5902561686278</v>
       </c>
       <c r="D97">
-        <v>1022.886597161355</v>
+        <v>738.8667038313722</v>
       </c>
       <c r="E97">
-        <v>1654.04495</v>
+        <v>1671.45596</v>
       </c>
       <c r="F97">
-        <v>1654.04595</v>
+        <v>1671.45696</v>
       </c>
       <c r="G97">
         <v>68</v>
@@ -9241,45 +9241,45 @@
         <v>194.4</v>
       </c>
       <c r="M97">
-        <v>242.81394546</v>
+        <v>335.628557568</v>
       </c>
       <c r="N97">
-        <v>-48.41394546000001</v>
+        <v>-141.228557568</v>
       </c>
       <c r="O97">
-        <v>-10.8931377285</v>
+        <v>-31.77642545280001</v>
       </c>
       <c r="P97">
-        <v>-37.52080773150001</v>
+        <v>-109.4521321152</v>
       </c>
       <c r="Q97">
-        <v>-27.72080773150002</v>
+        <v>-99.65213211520003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.370758804636192</v>
+        <v>1.793955616082686</v>
       </c>
       <c r="T97">
-        <v>9.238199152863453</v>
+        <v>12.18891461006818</v>
       </c>
       <c r="U97">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1801379237800224</v>
+        <v>0.1303226409485077</v>
       </c>
       <c r="W97">
-        <v>0.1203557527890927</v>
+        <v>0.1746312136975397</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.8006129945778774</v>
+        <v>0.579211737548923</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2394041897929454</v>
+        <v>0.2409541897929454</v>
       </c>
       <c r="C98">
-        <v>-864.5902561686278</v>
+        <v>-887.5841586252681</v>
       </c>
       <c r="D98">
-        <v>738.866703831372</v>
+        <v>733.2838113747317</v>
       </c>
       <c r="E98">
-        <v>1671.45596</v>
+        <v>1688.86697</v>
       </c>
       <c r="F98">
-        <v>1671.45696</v>
+        <v>1688.86797</v>
       </c>
       <c r="G98">
         <v>68</v>
@@ -9323,37 +9323,37 @@
         <v>194.4</v>
       </c>
       <c r="M98">
-        <v>335.628557568</v>
+        <v>339.124688376</v>
       </c>
       <c r="N98">
-        <v>-141.228557568</v>
+        <v>-144.724688376</v>
       </c>
       <c r="O98">
-        <v>-31.77642545279999</v>
+        <v>-32.5630548846</v>
       </c>
       <c r="P98">
-        <v>-109.4521321152</v>
+        <v>-112.1616334914</v>
       </c>
       <c r="Q98">
-        <v>-99.65213211519998</v>
+        <v>-102.3616334914</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.793955616082682</v>
+        <v>2.376674154776908</v>
       </c>
       <c r="T98">
-        <v>12.18891461006815</v>
+        <v>16.25188614675753</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1303226409485077</v>
+        <v>0.1289791085675952</v>
       </c>
       <c r="W98">
-        <v>0.1746312136975397</v>
+        <v>0.1749009949996269</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5792117375489231</v>
+        <v>0.5732404825226454</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2409541897929454</v>
+        <v>0.2425041897929454</v>
       </c>
       <c r="C99">
-        <v>-887.5841586252681</v>
+        <v>-910.4943248871741</v>
       </c>
       <c r="D99">
-        <v>733.2838113747317</v>
+        <v>727.7846551128257</v>
       </c>
       <c r="E99">
-        <v>1688.86697</v>
+        <v>1706.27798</v>
       </c>
       <c r="F99">
-        <v>1688.86797</v>
+        <v>1706.27898</v>
       </c>
       <c r="G99">
         <v>68</v>
@@ -9405,37 +9405,37 @@
         <v>194.4</v>
       </c>
       <c r="M99">
-        <v>339.124688376</v>
+        <v>342.620819184</v>
       </c>
       <c r="N99">
-        <v>-144.724688376</v>
+        <v>-148.220819184</v>
       </c>
       <c r="O99">
-        <v>-32.5630548846</v>
+        <v>-33.34968431639999</v>
       </c>
       <c r="P99">
-        <v>-112.1616334914</v>
+        <v>-114.8711348676</v>
       </c>
       <c r="Q99">
-        <v>-102.3616334914</v>
+        <v>-105.0711348676</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.376674154776908</v>
+        <v>3.542111232165362</v>
       </c>
       <c r="T99">
-        <v>16.25188614675753</v>
+        <v>24.3778292201363</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1289791085675952</v>
+        <v>0.1276629952148647</v>
       </c>
       <c r="W99">
-        <v>0.1749009949996269</v>
+        <v>0.1751652705608552</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5732404825226454</v>
+        <v>0.567391089843843</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2425041897929454</v>
+        <v>0.2440541897929454</v>
       </c>
       <c r="C100">
-        <v>-910.4943248871741</v>
+        <v>-933.3226248340251</v>
       </c>
       <c r="D100">
-        <v>727.7846551128257</v>
+        <v>722.3673651659748</v>
       </c>
       <c r="E100">
-        <v>1706.27798</v>
+        <v>1723.68899</v>
       </c>
       <c r="F100">
-        <v>1706.27898</v>
+        <v>1723.68999</v>
       </c>
       <c r="G100">
         <v>68</v>
@@ -9487,37 +9487,37 @@
         <v>194.4</v>
       </c>
       <c r="M100">
-        <v>342.620819184</v>
+        <v>346.116949992</v>
       </c>
       <c r="N100">
-        <v>-148.220819184</v>
+        <v>-151.716949992</v>
       </c>
       <c r="O100">
-        <v>-33.34968431639999</v>
+        <v>-34.1363137482</v>
       </c>
       <c r="P100">
-        <v>-114.8711348676</v>
+        <v>-117.5806362438</v>
       </c>
       <c r="Q100">
-        <v>-105.0711348676</v>
+        <v>-107.7806362438</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.542111232165362</v>
+        <v>7.038422464330726</v>
       </c>
       <c r="T100">
-        <v>24.3778292201363</v>
+        <v>48.7556584402726</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1276629952148647</v>
+        <v>0.1263734700106741</v>
       </c>
       <c r="W100">
-        <v>0.1751652705608552</v>
+        <v>0.1754242072218566</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.567391089843843</v>
+        <v>0.5616598667141071</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2440541897929454</v>
-      </c>
-      <c r="C101">
-        <v>-933.3226248340251</v>
-      </c>
-      <c r="D101">
-        <v>722.3673651659748</v>
-      </c>
-      <c r="E101">
-        <v>1723.68899</v>
-      </c>
-      <c r="F101">
-        <v>1723.68999</v>
-      </c>
-      <c r="G101">
-        <v>68</v>
-      </c>
-      <c r="H101">
-        <v>1741.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>204.2</v>
-      </c>
-      <c r="K101">
-        <v>9.799999999999983</v>
-      </c>
-      <c r="L101">
-        <v>194.4</v>
-      </c>
-      <c r="M101">
-        <v>346.116949992</v>
-      </c>
-      <c r="N101">
-        <v>-151.716949992</v>
-      </c>
-      <c r="O101">
-        <v>-34.1363137482</v>
-      </c>
-      <c r="P101">
-        <v>-117.5806362438</v>
-      </c>
-      <c r="Q101">
-        <v>-107.7806362438</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.038422464330726</v>
-      </c>
-      <c r="T101">
-        <v>48.7556584402726</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1263734700106741</v>
-      </c>
-      <c r="W101">
-        <v>0.1754242072218566</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5616598667141071</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
